--- a/zhimingganggu.xlsx
+++ b/zhimingganggu.xlsx
@@ -484,40 +484,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02359</t>
+          <t>00981</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>中芯国际</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>142</v>
+        <v>71.05</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>5.25</v>
       </c>
       <c r="F2" t="n">
-        <v>12.7</v>
+        <v>7.98</v>
       </c>
       <c r="G2" t="n">
-        <v>136.1</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>148</v>
+        <v>71.7</v>
       </c>
       <c r="I2" t="n">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="J2" t="n">
-        <v>126</v>
+        <v>65.8</v>
       </c>
       <c r="K2" t="n">
-        <v>18309692</v>
+        <v>155499374</v>
       </c>
       <c r="L2" t="n">
-        <v>2631383392</v>
+        <v>10768367360</v>
       </c>
     </row>
     <row r="3">
@@ -526,40 +526,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00168</t>
+          <t>01516</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>青岛啤酒股份</t>
+          <t>融创服务</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>52.6</v>
+        <v>1.05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>4.47</v>
+        <v>7.14</v>
       </c>
       <c r="G3" t="n">
-        <v>50.8</v>
+        <v>0.98</v>
       </c>
       <c r="H3" t="n">
-        <v>52.7</v>
+        <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>50.35</v>
+        <v>0.98</v>
       </c>
       <c r="J3" t="n">
-        <v>50.35</v>
+        <v>0.98</v>
       </c>
       <c r="K3" t="n">
-        <v>4580854</v>
+        <v>8149000</v>
       </c>
       <c r="L3" t="n">
-        <v>238449351</v>
+        <v>8315599</v>
       </c>
     </row>
     <row r="4">
@@ -568,40 +568,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01797</t>
+          <t>01347</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>东方甄选</t>
+          <t>华虹半导体</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.78</v>
+        <v>114.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.92</v>
+        <v>6.5</v>
       </c>
       <c r="F4" t="n">
-        <v>3.43</v>
+        <v>6.01</v>
       </c>
       <c r="G4" t="n">
-        <v>27.06</v>
+        <v>109</v>
       </c>
       <c r="H4" t="n">
-        <v>27.92</v>
+        <v>117.3</v>
       </c>
       <c r="I4" t="n">
-        <v>26.62</v>
+        <v>103</v>
       </c>
       <c r="J4" t="n">
-        <v>26.86</v>
+        <v>108.1</v>
       </c>
       <c r="K4" t="n">
-        <v>7227028</v>
+        <v>58437352</v>
       </c>
       <c r="L4" t="n">
-        <v>196655089</v>
+        <v>6432826112</v>
       </c>
     </row>
     <row r="5">
@@ -610,40 +610,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>00656</t>
+          <t>09696</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>复星国际</t>
+          <t>天齐锂业</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.14</v>
+        <v>66.3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>3.05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.99</v>
+        <v>4.82</v>
       </c>
       <c r="G5" t="n">
-        <v>4.01</v>
+        <v>63.2</v>
       </c>
       <c r="H5" t="n">
-        <v>4.17</v>
+        <v>67.75</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>62.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4.02</v>
+        <v>63.25</v>
       </c>
       <c r="K5" t="n">
-        <v>10147247</v>
+        <v>16550110</v>
       </c>
       <c r="L5" t="n">
-        <v>41701154</v>
+        <v>1089991824</v>
       </c>
     </row>
     <row r="6">
@@ -652,40 +652,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01579</t>
+          <t>02628</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>颐海国际</t>
+          <t>中国人寿</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.05</v>
+        <v>28.64</v>
       </c>
       <c r="E6" t="n">
-        <v>0.46</v>
+        <v>1.24</v>
       </c>
       <c r="F6" t="n">
-        <v>2.95</v>
+        <v>4.53</v>
       </c>
       <c r="G6" t="n">
-        <v>15.66</v>
+        <v>28.5</v>
       </c>
       <c r="H6" t="n">
-        <v>16.06</v>
+        <v>29.18</v>
       </c>
       <c r="I6" t="n">
-        <v>15.29</v>
+        <v>28.22</v>
       </c>
       <c r="J6" t="n">
-        <v>15.59</v>
+        <v>27.4</v>
       </c>
       <c r="K6" t="n">
-        <v>2292000</v>
+        <v>88216758</v>
       </c>
       <c r="L6" t="n">
-        <v>36219135</v>
+        <v>2534612912</v>
       </c>
     </row>
     <row r="7">
@@ -694,40 +694,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06690</t>
+          <t>01918</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>海尔智家</t>
+          <t>融创中国</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.4</v>
+        <v>1.15</v>
       </c>
       <c r="E7" t="n">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>2.59</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>20.54</v>
+        <v>1.11</v>
       </c>
       <c r="H7" t="n">
-        <v>21.68</v>
+        <v>1.17</v>
       </c>
       <c r="I7" t="n">
-        <v>20.42</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
-        <v>20.86</v>
+        <v>1.11</v>
       </c>
       <c r="K7" t="n">
-        <v>23014728</v>
+        <v>270440528</v>
       </c>
       <c r="L7" t="n">
-        <v>491388960</v>
+        <v>308209472</v>
       </c>
     </row>
     <row r="8">
@@ -736,40 +736,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>00883</t>
+          <t>02319</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>中国海洋石油</t>
+          <t>蒙牛乳业</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.02</v>
+        <v>17.26</v>
       </c>
       <c r="E8" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="G8" t="n">
-        <v>28.24</v>
+        <v>16.95</v>
       </c>
       <c r="H8" t="n">
-        <v>29.06</v>
+        <v>17.5</v>
       </c>
       <c r="I8" t="n">
-        <v>28.2</v>
+        <v>16.76</v>
       </c>
       <c r="J8" t="n">
-        <v>28.44</v>
+        <v>16.7</v>
       </c>
       <c r="K8" t="n">
-        <v>72070102</v>
+        <v>30114827</v>
       </c>
       <c r="L8" t="n">
-        <v>2074228560</v>
+        <v>518692320</v>
       </c>
     </row>
     <row r="9">
@@ -778,40 +778,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>02269</t>
+          <t>00175</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>药明生物</t>
+          <t>吉利汽车</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>33.66</v>
+        <v>22.9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>2.51</v>
       </c>
       <c r="G9" t="n">
-        <v>34</v>
+        <v>22.88</v>
       </c>
       <c r="H9" t="n">
-        <v>35.26</v>
+        <v>23.3</v>
       </c>
       <c r="I9" t="n">
-        <v>33.42</v>
+        <v>22.08</v>
       </c>
       <c r="J9" t="n">
-        <v>33.28</v>
+        <v>22.34</v>
       </c>
       <c r="K9" t="n">
-        <v>33916793</v>
+        <v>82040697</v>
       </c>
       <c r="L9" t="n">
-        <v>1164360112</v>
+        <v>1863163440</v>
       </c>
     </row>
     <row r="10">
@@ -820,40 +820,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>09999</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中国电信</t>
+          <t>网易-S</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.19</v>
+        <v>179.2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05</v>
+        <v>4.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.97</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>5.13</v>
+        <v>178.1</v>
       </c>
       <c r="H10" t="n">
-        <v>5.24</v>
+        <v>180.3</v>
       </c>
       <c r="I10" t="n">
-        <v>5.11</v>
+        <v>177.7</v>
       </c>
       <c r="J10" t="n">
-        <v>5.14</v>
+        <v>175</v>
       </c>
       <c r="K10" t="n">
-        <v>64207110</v>
+        <v>8736682</v>
       </c>
       <c r="L10" t="n">
-        <v>333063584</v>
+        <v>1560520496</v>
       </c>
     </row>
     <row r="11">
@@ -862,40 +862,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01918</t>
+          <t>00291</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>融创中国</t>
+          <t>华润啤酒</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.06</v>
+        <v>26.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01</v>
+        <v>0.62</v>
       </c>
       <c r="F11" t="n">
-        <v>0.95</v>
+        <v>2.37</v>
       </c>
       <c r="G11" t="n">
-        <v>1.05</v>
+        <v>26.16</v>
       </c>
       <c r="H11" t="n">
-        <v>1.07</v>
+        <v>26.96</v>
       </c>
       <c r="I11" t="n">
-        <v>1.05</v>
+        <v>26.06</v>
       </c>
       <c r="J11" t="n">
-        <v>1.05</v>
+        <v>26.18</v>
       </c>
       <c r="K11" t="n">
-        <v>51874000</v>
+        <v>20272525</v>
       </c>
       <c r="L11" t="n">
-        <v>55019960</v>
+        <v>538421680</v>
       </c>
     </row>
     <row r="12">
@@ -904,40 +904,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>00322</t>
+          <t>00873</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>康师傅控股</t>
+          <t>世茂服务</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.56</v>
+        <v>0.6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8</v>
+        <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>12.47</v>
+        <v>0.59</v>
       </c>
       <c r="H12" t="n">
-        <v>12.66</v>
+        <v>0.63</v>
       </c>
       <c r="I12" t="n">
-        <v>12.22</v>
+        <v>0.59</v>
       </c>
       <c r="J12" t="n">
-        <v>12.46</v>
+        <v>0.59</v>
       </c>
       <c r="K12" t="n">
-        <v>10165081</v>
+        <v>1353000</v>
       </c>
       <c r="L12" t="n">
-        <v>127509592</v>
+        <v>819630</v>
       </c>
     </row>
     <row r="13">
@@ -946,40 +946,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09901</t>
+          <t>00268</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>新东方-S</t>
+          <t>金蝶国际</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41.22</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="F13" t="n">
-        <v>0.78</v>
+        <v>1.07</v>
       </c>
       <c r="G13" t="n">
-        <v>40.9</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>42.28</v>
+        <v>8.58</v>
       </c>
       <c r="I13" t="n">
-        <v>40.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>40.9</v>
+        <v>8.44</v>
       </c>
       <c r="K13" t="n">
-        <v>2616566</v>
+        <v>33873920</v>
       </c>
       <c r="L13" t="n">
-        <v>108511026</v>
+        <v>287360144</v>
       </c>
     </row>
     <row r="14">
@@ -988,40 +988,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>06186</t>
+          <t>00763</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中国飞鹤</t>
+          <t>中兴通讯</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.49</v>
+        <v>24.94</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.58</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>3.49</v>
+        <v>24.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>25.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3.44</v>
+        <v>24.22</v>
       </c>
       <c r="J14" t="n">
-        <v>3.47</v>
+        <v>24.74</v>
       </c>
       <c r="K14" t="n">
-        <v>9295000</v>
+        <v>17083488</v>
       </c>
       <c r="L14" t="n">
-        <v>32268993</v>
+        <v>421246224</v>
       </c>
     </row>
     <row r="15">
@@ -1030,40 +1030,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>00941</t>
+          <t>01816</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>中广核电力</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>84.8</v>
+        <v>3.46</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="G15" t="n">
-        <v>84.2</v>
+        <v>3.43</v>
       </c>
       <c r="H15" t="n">
-        <v>84.90000000000001</v>
+        <v>3.49</v>
       </c>
       <c r="I15" t="n">
-        <v>83.8</v>
+        <v>3.41</v>
       </c>
       <c r="J15" t="n">
-        <v>84.40000000000001</v>
+        <v>3.44</v>
       </c>
       <c r="K15" t="n">
-        <v>13278941</v>
+        <v>57691000</v>
       </c>
       <c r="L15" t="n">
-        <v>1123564000</v>
+        <v>200077537</v>
       </c>
     </row>
     <row r="16">
@@ -1072,40 +1072,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>02196</t>
+          <t>09992</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>复星医药</t>
+          <t>泡泡玛特</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19.79</v>
+        <v>157.6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
       <c r="G16" t="n">
-        <v>19.55</v>
+        <v>155.9</v>
       </c>
       <c r="H16" t="n">
-        <v>20.36</v>
+        <v>159.5</v>
       </c>
       <c r="I16" t="n">
-        <v>19.55</v>
+        <v>154.3</v>
       </c>
       <c r="J16" t="n">
-        <v>19.71</v>
+        <v>156.8</v>
       </c>
       <c r="K16" t="n">
-        <v>1607512</v>
+        <v>11642684</v>
       </c>
       <c r="L16" t="n">
-        <v>32080419</v>
+        <v>1823918416</v>
       </c>
     </row>
     <row r="17">
@@ -1114,40 +1114,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>00291</t>
+          <t>09961</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>华润啤酒</t>
+          <t>携程集团-S</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.44</v>
+        <v>419.2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="G17" t="n">
-        <v>25.3</v>
+        <v>415.2</v>
       </c>
       <c r="H17" t="n">
-        <v>25.54</v>
+        <v>419.6</v>
       </c>
       <c r="I17" t="n">
-        <v>25.12</v>
+        <v>414.4</v>
       </c>
       <c r="J17" t="n">
-        <v>25.34</v>
+        <v>417.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4164323</v>
+        <v>1311444</v>
       </c>
       <c r="L17" t="n">
-        <v>105619939</v>
+        <v>547657088</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>00016</t>
+          <t>02423</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新鸿基地产</t>
+          <t>贝壳-W</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>136.9</v>
+        <v>42.32</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="F18" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="G18" t="n">
-        <v>136.4</v>
+        <v>42.04</v>
       </c>
       <c r="H18" t="n">
-        <v>138.3</v>
+        <v>43.32</v>
       </c>
       <c r="I18" t="n">
-        <v>136.4</v>
+        <v>41.46</v>
       </c>
       <c r="J18" t="n">
-        <v>136.4</v>
+        <v>42.16</v>
       </c>
       <c r="K18" t="n">
-        <v>1370088</v>
+        <v>10005400</v>
       </c>
       <c r="L18" t="n">
-        <v>187857193</v>
+        <v>427832896</v>
       </c>
     </row>
     <row r="19">
@@ -1198,40 +1198,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>02618</t>
+          <t>09987</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>京东物流</t>
+          <t>百胜中国</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.13</v>
+        <v>380.6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04</v>
+        <v>1.4</v>
       </c>
       <c r="F19" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="G19" t="n">
-        <v>15.31</v>
+        <v>383</v>
       </c>
       <c r="H19" t="n">
-        <v>15.31</v>
+        <v>392</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>377.2</v>
       </c>
       <c r="J19" t="n">
-        <v>15.09</v>
+        <v>379.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3687692</v>
+        <v>742209</v>
       </c>
       <c r="L19" t="n">
-        <v>55753579</v>
+        <v>283798688</v>
       </c>
     </row>
     <row r="20">
@@ -1240,40 +1240,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01876</t>
+          <t>03690</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>百威亚太</t>
+          <t>美团-W</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7.55</v>
+        <v>83.45</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01</v>
+        <v>0.3</v>
       </c>
       <c r="F20" t="n">
-        <v>0.13</v>
+        <v>0.36</v>
       </c>
       <c r="G20" t="n">
-        <v>7.45</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>7.56</v>
+        <v>84.5</v>
       </c>
       <c r="I20" t="n">
-        <v>7.45</v>
+        <v>81.25</v>
       </c>
       <c r="J20" t="n">
-        <v>7.54</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>3338978</v>
+        <v>38275724</v>
       </c>
       <c r="L20" t="n">
-        <v>25066713</v>
+        <v>3174579760</v>
       </c>
     </row>
     <row r="21">
@@ -1282,40 +1282,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09999</t>
+          <t>01093</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>网易-S</t>
+          <t>石药集团</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>173.5</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="F21" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="G21" t="n">
-        <v>177.2</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>177.2</v>
+        <v>8.44</v>
       </c>
       <c r="I21" t="n">
-        <v>173.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>173.3</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>2869666</v>
+        <v>78219716</v>
       </c>
       <c r="L21" t="n">
-        <v>500869568</v>
+        <v>650579328</v>
       </c>
     </row>
     <row r="22">
@@ -1324,40 +1324,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09961</t>
+          <t>02007</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>携程集团-S</t>
+          <t>碧桂园</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>410</v>
+        <v>0.285</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>411.2</v>
+        <v>0.285</v>
       </c>
       <c r="H22" t="n">
-        <v>416.8</v>
+        <v>0.295</v>
       </c>
       <c r="I22" t="n">
-        <v>410</v>
+        <v>0.28</v>
       </c>
       <c r="J22" t="n">
-        <v>409.6</v>
+        <v>0.285</v>
       </c>
       <c r="K22" t="n">
-        <v>1103244</v>
+        <v>263479228</v>
       </c>
       <c r="L22" t="n">
-        <v>455944928</v>
+        <v>75855644</v>
       </c>
     </row>
     <row r="23">
@@ -1366,40 +1366,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01299</t>
+          <t>00656</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>友邦保险</t>
+          <t>复星国际</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>83.25</v>
+        <v>4.12</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>83.8</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="n">
-        <v>84.15000000000001</v>
+        <v>4.16</v>
       </c>
       <c r="I23" t="n">
-        <v>83.09999999999999</v>
+        <v>4.05</v>
       </c>
       <c r="J23" t="n">
-        <v>83.2</v>
+        <v>4.12</v>
       </c>
       <c r="K23" t="n">
-        <v>13250852</v>
+        <v>10344364</v>
       </c>
       <c r="L23" t="n">
-        <v>1107409840</v>
+        <v>42437499</v>
       </c>
     </row>
     <row r="24">
@@ -1408,16 +1408,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>06098</t>
+          <t>00520</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>碧桂园服务</t>
+          <t>呷哺呷哺</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6.11</v>
+        <v>0.41</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1426,22 +1426,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>6.11</v>
+        <v>0.415</v>
       </c>
       <c r="H24" t="n">
-        <v>6.15</v>
+        <v>0.425</v>
       </c>
       <c r="I24" t="n">
-        <v>6.08</v>
+        <v>0.41</v>
       </c>
       <c r="J24" t="n">
-        <v>6.11</v>
+        <v>0.41</v>
       </c>
       <c r="K24" t="n">
-        <v>2288114</v>
+        <v>4046500</v>
       </c>
       <c r="L24" t="n">
-        <v>13980887</v>
+        <v>1674637</v>
       </c>
     </row>
     <row r="25">
@@ -1450,40 +1450,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03998</t>
+          <t>01299</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>波司登</t>
+          <t>友邦保险</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.31</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="G25" t="n">
-        <v>4.29</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>4.31</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>4.24</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>4.31</v>
+        <v>84.95</v>
       </c>
       <c r="K25" t="n">
-        <v>12415015</v>
+        <v>25042541</v>
       </c>
       <c r="L25" t="n">
-        <v>53125790</v>
+        <v>2144556144</v>
       </c>
     </row>
     <row r="26">
@@ -1492,40 +1492,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03988</t>
+          <t>00751</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>中国银行</t>
+          <t>创维集团</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.12</v>
+        <v>6.25</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0.16</v>
       </c>
       <c r="G26" t="n">
-        <v>5.1</v>
+        <v>6.21</v>
       </c>
       <c r="H26" t="n">
-        <v>5.12</v>
+        <v>6.26</v>
       </c>
       <c r="I26" t="n">
-        <v>5.06</v>
+        <v>6.21</v>
       </c>
       <c r="J26" t="n">
-        <v>5.12</v>
+        <v>6.26</v>
       </c>
       <c r="K26" t="n">
-        <v>97785258</v>
+        <v>540110</v>
       </c>
       <c r="L26" t="n">
-        <v>497689264</v>
+        <v>3368599</v>
       </c>
     </row>
     <row r="27">
@@ -1534,40 +1534,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03900</t>
+          <t>01772</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>绿城中国</t>
+          <t>赣锋锂业</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9.06</v>
+        <v>83.8</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="G27" t="n">
-        <v>9.1</v>
+        <v>84.2</v>
       </c>
       <c r="H27" t="n">
-        <v>9.220000000000001</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>9.01</v>
+        <v>82.5</v>
       </c>
       <c r="J27" t="n">
-        <v>9.06</v>
+        <v>83.95</v>
       </c>
       <c r="K27" t="n">
-        <v>4400000</v>
+        <v>14093676</v>
       </c>
       <c r="L27" t="n">
-        <v>39958087</v>
+        <v>1193971168</v>
       </c>
     </row>
     <row r="28">
@@ -1576,40 +1576,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>02007</t>
+          <t>00168</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>碧桂园</t>
+          <t>青岛啤酒股份</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.28</v>
+        <v>53.9</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="G28" t="n">
-        <v>0.275</v>
+        <v>53.35</v>
       </c>
       <c r="H28" t="n">
-        <v>0.28</v>
+        <v>54.25</v>
       </c>
       <c r="I28" t="n">
-        <v>0.27</v>
+        <v>53.35</v>
       </c>
       <c r="J28" t="n">
-        <v>0.28</v>
+        <v>54</v>
       </c>
       <c r="K28" t="n">
-        <v>100310000</v>
+        <v>3332698</v>
       </c>
       <c r="L28" t="n">
-        <v>27737090</v>
+        <v>179334798</v>
       </c>
     </row>
     <row r="29">
@@ -1618,40 +1618,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01816</t>
+          <t>00285</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>中广核电力</t>
+          <t>比亚迪电子</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3.48</v>
+        <v>26.54</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="G29" t="n">
-        <v>3.5</v>
+        <v>26.42</v>
       </c>
       <c r="H29" t="n">
-        <v>3.51</v>
+        <v>26.88</v>
       </c>
       <c r="I29" t="n">
-        <v>3.44</v>
+        <v>26.12</v>
       </c>
       <c r="J29" t="n">
-        <v>3.48</v>
+        <v>26.6</v>
       </c>
       <c r="K29" t="n">
-        <v>49109030</v>
+        <v>8655279</v>
       </c>
       <c r="L29" t="n">
-        <v>170952599</v>
+        <v>229675835</v>
       </c>
     </row>
     <row r="30">
@@ -1660,40 +1660,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01516</t>
+          <t>01179</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>融创服务</t>
+          <t>华住集团-S</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.93</v>
+        <v>39.98</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="G30" t="n">
-        <v>0.92</v>
+        <v>40.1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9399999999999999</v>
+        <v>40.7</v>
       </c>
       <c r="I30" t="n">
-        <v>0.92</v>
+        <v>39.94</v>
       </c>
       <c r="J30" t="n">
-        <v>0.93</v>
+        <v>40.08</v>
       </c>
       <c r="K30" t="n">
-        <v>1221511</v>
+        <v>1712750</v>
       </c>
       <c r="L30" t="n">
-        <v>1132289</v>
+        <v>68880204</v>
       </c>
     </row>
     <row r="31">
@@ -1702,40 +1702,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01458</t>
+          <t>06862</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>周黑鸭</t>
+          <t>海底捞</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.44</v>
+        <v>14.32</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="G31" t="n">
-        <v>1.44</v>
+        <v>14.36</v>
       </c>
       <c r="H31" t="n">
-        <v>1.46</v>
+        <v>14.5</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>14.29</v>
       </c>
       <c r="J31" t="n">
-        <v>1.44</v>
+        <v>14.36</v>
       </c>
       <c r="K31" t="n">
-        <v>1586500</v>
+        <v>7411975</v>
       </c>
       <c r="L31" t="n">
-        <v>2265526</v>
+        <v>106543785</v>
       </c>
     </row>
     <row r="32">
@@ -1744,40 +1744,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>00873</t>
+          <t>01876</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>世茂服务</t>
+          <t>百威亚太</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.68</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.66</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.72</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="K32" t="n">
-        <v>113057</v>
+        <v>10281900</v>
       </c>
       <c r="L32" t="n">
-        <v>63311</v>
+        <v>78454907</v>
       </c>
     </row>
     <row r="33">
@@ -1786,40 +1786,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>00762</t>
+          <t>02382</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>中国联通</t>
+          <t>舜宇光学科技</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7.33</v>
+        <v>63.6</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="G33" t="n">
-        <v>7.3</v>
+        <v>63</v>
       </c>
       <c r="H33" t="n">
-        <v>7.37</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>7.28</v>
+        <v>62.6</v>
       </c>
       <c r="J33" t="n">
-        <v>7.33</v>
+        <v>63.85</v>
       </c>
       <c r="K33" t="n">
-        <v>7847266</v>
+        <v>7941894</v>
       </c>
       <c r="L33" t="n">
-        <v>57511652</v>
+        <v>503184128</v>
       </c>
     </row>
     <row r="34">
@@ -1828,40 +1828,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>00520</t>
+          <t>00909</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>呷哺呷哺</t>
+          <t>明源云</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.41</v>
+        <v>2.1</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="G34" t="n">
-        <v>0.41</v>
+        <v>2.12</v>
       </c>
       <c r="H34" t="n">
-        <v>0.415</v>
+        <v>2.12</v>
       </c>
       <c r="I34" t="n">
-        <v>0.41</v>
+        <v>2.09</v>
       </c>
       <c r="J34" t="n">
-        <v>0.41</v>
+        <v>2.11</v>
       </c>
       <c r="K34" t="n">
-        <v>463000</v>
+        <v>2558000</v>
       </c>
       <c r="L34" t="n">
-        <v>190270</v>
+        <v>5371084</v>
       </c>
     </row>
     <row r="35">
@@ -1870,40 +1870,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>00493</t>
+          <t>00883</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>国美零售</t>
+          <t>中国海洋石油</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.014</v>
+        <v>29.24</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-0.48</v>
       </c>
       <c r="G35" t="n">
-        <v>0.013</v>
+        <v>29.6</v>
       </c>
       <c r="H35" t="n">
-        <v>0.014</v>
+        <v>29.8</v>
       </c>
       <c r="I35" t="n">
-        <v>0.013</v>
+        <v>29.08</v>
       </c>
       <c r="J35" t="n">
-        <v>0.014</v>
+        <v>29.38</v>
       </c>
       <c r="K35" t="n">
-        <v>13703002</v>
+        <v>90890158</v>
       </c>
       <c r="L35" t="n">
-        <v>178790</v>
+        <v>2671668848</v>
       </c>
     </row>
     <row r="36">
@@ -1912,40 +1912,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>00005</t>
+          <t>00998</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>汇丰控股</t>
+          <t>中信银行</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>140.1</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="G36" t="n">
-        <v>139.6</v>
+        <v>8.34</v>
       </c>
       <c r="H36" t="n">
-        <v>140.7</v>
+        <v>8.4</v>
       </c>
       <c r="I36" t="n">
-        <v>139.6</v>
+        <v>8.06</v>
       </c>
       <c r="J36" t="n">
-        <v>140.2</v>
+        <v>8.26</v>
       </c>
       <c r="K36" t="n">
-        <v>3484784</v>
+        <v>53891018</v>
       </c>
       <c r="L36" t="n">
-        <v>488065440</v>
+        <v>442009552</v>
       </c>
     </row>
     <row r="37">
@@ -1954,40 +1954,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>00788</t>
+          <t>01896</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>中国铁塔</t>
+          <t>猫眼娱乐</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>5.96</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.09</v>
+        <v>-0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>11.11</v>
+        <v>5.99</v>
       </c>
       <c r="H37" t="n">
-        <v>11.14</v>
+        <v>6.02</v>
       </c>
       <c r="I37" t="n">
-        <v>11.02</v>
+        <v>5.89</v>
       </c>
       <c r="J37" t="n">
-        <v>11.11</v>
+        <v>5.99</v>
       </c>
       <c r="K37" t="n">
-        <v>5135628</v>
+        <v>27944600</v>
       </c>
       <c r="L37" t="n">
-        <v>56979354</v>
+        <v>158509709</v>
       </c>
     </row>
     <row r="38">
@@ -1996,40 +1996,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>00939</t>
+          <t>00020</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>商汤-W</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8.880000000000001</v>
+        <v>1.98</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.22</v>
+        <v>-0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>8.84</v>
+        <v>1.97</v>
       </c>
       <c r="H38" t="n">
-        <v>8.880000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="I38" t="n">
-        <v>8.779999999999999</v>
+        <v>1.93</v>
       </c>
       <c r="J38" t="n">
-        <v>8.9</v>
+        <v>1.99</v>
       </c>
       <c r="K38" t="n">
-        <v>136694884</v>
+        <v>321491008</v>
       </c>
       <c r="L38" t="n">
-        <v>1208950528</v>
+        <v>631012480</v>
       </c>
     </row>
     <row r="39">
@@ -2038,40 +2038,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01288</t>
+          <t>01928</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>农业银行</t>
+          <t>金沙中国有限公司</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6.15</v>
+        <v>16.25</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.32</v>
+        <v>-0.55</v>
       </c>
       <c r="G39" t="n">
-        <v>6.17</v>
+        <v>16.24</v>
       </c>
       <c r="H39" t="n">
-        <v>6.18</v>
+        <v>16.29</v>
       </c>
       <c r="I39" t="n">
-        <v>6.06</v>
+        <v>15.96</v>
       </c>
       <c r="J39" t="n">
-        <v>6.17</v>
+        <v>16.34</v>
       </c>
       <c r="K39" t="n">
-        <v>150527279</v>
+        <v>7338824</v>
       </c>
       <c r="L39" t="n">
-        <v>923045104</v>
+        <v>118167476</v>
       </c>
     </row>
     <row r="40">
@@ -2080,40 +2080,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>02202</t>
+          <t>06186</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>万科企业</t>
+          <t>中国飞鹤</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.84</v>
+        <v>3.49</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.35</v>
+        <v>-0.57</v>
       </c>
       <c r="G40" t="n">
-        <v>2.85</v>
+        <v>3.51</v>
       </c>
       <c r="H40" t="n">
-        <v>2.9</v>
+        <v>3.51</v>
       </c>
       <c r="I40" t="n">
-        <v>2.83</v>
+        <v>3.48</v>
       </c>
       <c r="J40" t="n">
-        <v>2.85</v>
+        <v>3.51</v>
       </c>
       <c r="K40" t="n">
-        <v>13316521</v>
+        <v>7009800</v>
       </c>
       <c r="L40" t="n">
-        <v>38170193</v>
+        <v>24481675</v>
       </c>
     </row>
     <row r="41">
@@ -2122,40 +2122,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>06049</t>
+          <t>09888</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>保利物业</t>
+          <t>百度集团-SW</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>30.7</v>
+        <v>119.2</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.14</v>
+        <v>-0.7</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.45</v>
+        <v>-0.58</v>
       </c>
       <c r="G41" t="n">
-        <v>30.8</v>
+        <v>118.6</v>
       </c>
       <c r="H41" t="n">
-        <v>31.14</v>
+        <v>119.8</v>
       </c>
       <c r="I41" t="n">
-        <v>30.68</v>
+        <v>117</v>
       </c>
       <c r="J41" t="n">
-        <v>30.84</v>
+        <v>119.9</v>
       </c>
       <c r="K41" t="n">
-        <v>499000</v>
+        <v>6899370</v>
       </c>
       <c r="L41" t="n">
-        <v>15341004</v>
+        <v>816262944</v>
       </c>
     </row>
     <row r="42">
@@ -2164,40 +2164,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01398</t>
+          <t>03900</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>工商银行</t>
+          <t>绿城中国</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7.18</v>
+        <v>9.66</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.55</v>
+        <v>-0.62</v>
       </c>
       <c r="G42" t="n">
-        <v>7.18</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>7.22</v>
+        <v>9.94</v>
       </c>
       <c r="I42" t="n">
-        <v>7.06</v>
+        <v>9.65</v>
       </c>
       <c r="J42" t="n">
-        <v>7.22</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>210618005</v>
+        <v>9379227</v>
       </c>
       <c r="L42" t="n">
-        <v>1500071792</v>
+        <v>91640177</v>
       </c>
     </row>
     <row r="43">
@@ -2206,40 +2206,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>03328</t>
+          <t>01458</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>交通银行</t>
+          <t>周黑鸭</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7.31</v>
+        <v>1.5</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.68</v>
+        <v>-0.66</v>
       </c>
       <c r="G43" t="n">
-        <v>7.36</v>
+        <v>1.49</v>
       </c>
       <c r="H43" t="n">
-        <v>7.36</v>
+        <v>1.51</v>
       </c>
       <c r="I43" t="n">
-        <v>7.25</v>
+        <v>1.47</v>
       </c>
       <c r="J43" t="n">
-        <v>7.36</v>
+        <v>1.51</v>
       </c>
       <c r="K43" t="n">
-        <v>15829820</v>
+        <v>2166500</v>
       </c>
       <c r="L43" t="n">
-        <v>115428099</v>
+        <v>3226155</v>
       </c>
     </row>
     <row r="44">
@@ -2248,40 +2248,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>06185</t>
+          <t>02013</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>康希诺生物</t>
+          <t>微盟集团</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>32.08</v>
+        <v>1.46</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.22</v>
+        <v>-0.01</v>
       </c>
       <c r="F44" t="n">
         <v>-0.68</v>
       </c>
       <c r="G44" t="n">
-        <v>32.3</v>
+        <v>1.47</v>
       </c>
       <c r="H44" t="n">
-        <v>34.18</v>
+        <v>1.47</v>
       </c>
       <c r="I44" t="n">
-        <v>32.04</v>
+        <v>1.44</v>
       </c>
       <c r="J44" t="n">
-        <v>32.3</v>
+        <v>1.47</v>
       </c>
       <c r="K44" t="n">
-        <v>1048400</v>
+        <v>18872000</v>
       </c>
       <c r="L44" t="n">
-        <v>34560860</v>
+        <v>27487894</v>
       </c>
     </row>
     <row r="45">
@@ -2290,40 +2290,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>09696</t>
+          <t>06865</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>天齐锂业</t>
+          <t>福莱特玻璃</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>58.3</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.68</v>
+        <v>-0.77</v>
       </c>
       <c r="G45" t="n">
-        <v>60.15</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>60.95</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>57.6</v>
+        <v>8.93</v>
       </c>
       <c r="J45" t="n">
-        <v>58.7</v>
+        <v>9.07</v>
       </c>
       <c r="K45" t="n">
-        <v>5073668</v>
+        <v>2238500</v>
       </c>
       <c r="L45" t="n">
-        <v>298574640</v>
+        <v>20223970</v>
       </c>
     </row>
     <row r="46">
@@ -2332,40 +2332,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02331</t>
+          <t>00005</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>李宁</t>
+          <t>汇丰控股</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>20.08</v>
+        <v>139.9</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.14</v>
+        <v>-1.1</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.78</v>
       </c>
       <c r="G46" t="n">
-        <v>20.18</v>
+        <v>139.8</v>
       </c>
       <c r="H46" t="n">
-        <v>20.28</v>
+        <v>141.1</v>
       </c>
       <c r="I46" t="n">
-        <v>19.98</v>
+        <v>139.1</v>
       </c>
       <c r="J46" t="n">
-        <v>20.22</v>
+        <v>141</v>
       </c>
       <c r="K46" t="n">
-        <v>9742359</v>
+        <v>16202407</v>
       </c>
       <c r="L46" t="n">
-        <v>195906229</v>
+        <v>2272311232</v>
       </c>
     </row>
     <row r="47">
@@ -2374,40 +2374,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01347</t>
+          <t>06098</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>华虹半导体</t>
+          <t>碧桂园服务</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>113.8</v>
+        <v>6.22</v>
       </c>
       <c r="E47" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F47" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F47" t="n">
-        <v>-0.7</v>
-      </c>
       <c r="G47" t="n">
-        <v>113.6</v>
+        <v>6.25</v>
       </c>
       <c r="H47" t="n">
-        <v>119.6</v>
+        <v>6.29</v>
       </c>
       <c r="I47" t="n">
-        <v>112.2</v>
+        <v>6.2</v>
       </c>
       <c r="J47" t="n">
-        <v>114.6</v>
+        <v>6.27</v>
       </c>
       <c r="K47" t="n">
-        <v>25763239</v>
+        <v>2772054</v>
       </c>
       <c r="L47" t="n">
-        <v>2995113296</v>
+        <v>17312634</v>
       </c>
     </row>
     <row r="48">
@@ -2416,40 +2416,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>03968</t>
+          <t>06049</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>保利物业</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>49.96</v>
+        <v>31.16</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.39</v>
+        <v>-0.26</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.77</v>
+        <v>-0.83</v>
       </c>
       <c r="G48" t="n">
-        <v>50.3</v>
+        <v>31.48</v>
       </c>
       <c r="H48" t="n">
-        <v>50.45</v>
+        <v>31.66</v>
       </c>
       <c r="I48" t="n">
-        <v>49.54</v>
+        <v>31.1</v>
       </c>
       <c r="J48" t="n">
-        <v>50.35</v>
+        <v>31.42</v>
       </c>
       <c r="K48" t="n">
-        <v>10628350</v>
+        <v>597200</v>
       </c>
       <c r="L48" t="n">
-        <v>530242336</v>
+        <v>18698717</v>
       </c>
     </row>
     <row r="49">
@@ -2458,40 +2458,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>02057</t>
+          <t>09618</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>中通快递-W</t>
+          <t>京东集团-SW</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>201.8</v>
+        <v>116.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.6</v>
+        <v>-1</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.79</v>
+        <v>-0.85</v>
       </c>
       <c r="G49" t="n">
-        <v>200.4</v>
+        <v>115.8</v>
       </c>
       <c r="H49" t="n">
-        <v>202.4</v>
+        <v>117.5</v>
       </c>
       <c r="I49" t="n">
-        <v>199.3</v>
+        <v>115.6</v>
       </c>
       <c r="J49" t="n">
-        <v>203.4</v>
+        <v>117.5</v>
       </c>
       <c r="K49" t="n">
-        <v>1157264</v>
+        <v>3121255</v>
       </c>
       <c r="L49" t="n">
-        <v>232243856</v>
+        <v>363139328</v>
       </c>
     </row>
     <row r="50">
@@ -2500,40 +2500,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01658</t>
+          <t>01833</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>邮储银行</t>
+          <t>平安好医生</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5.21</v>
+        <v>10.74</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.95</v>
+        <v>-1.01</v>
       </c>
       <c r="G50" t="n">
-        <v>5.26</v>
+        <v>10.68</v>
       </c>
       <c r="H50" t="n">
-        <v>5.28</v>
+        <v>10.9</v>
       </c>
       <c r="I50" t="n">
-        <v>5.18</v>
+        <v>10.62</v>
       </c>
       <c r="J50" t="n">
-        <v>5.26</v>
+        <v>10.85</v>
       </c>
       <c r="K50" t="n">
-        <v>25634801</v>
+        <v>4868942</v>
       </c>
       <c r="L50" t="n">
-        <v>133761035</v>
+        <v>52174777</v>
       </c>
     </row>
     <row r="51">
@@ -2542,40 +2542,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>00388</t>
+          <t>09901</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>香港交易所</t>
+          <t>新东方-S</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>408</v>
+        <v>41.9</v>
       </c>
       <c r="E51" t="n">
-        <v>-4</v>
+        <v>-0.46</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.97</v>
+        <v>-1.09</v>
       </c>
       <c r="G51" t="n">
-        <v>409.6</v>
+        <v>42.34</v>
       </c>
       <c r="H51" t="n">
-        <v>414.8</v>
+        <v>42.38</v>
       </c>
       <c r="I51" t="n">
-        <v>407.2</v>
+        <v>41.44</v>
       </c>
       <c r="J51" t="n">
-        <v>412</v>
+        <v>42.36</v>
       </c>
       <c r="K51" t="n">
-        <v>2382580</v>
+        <v>3243759</v>
       </c>
       <c r="L51" t="n">
-        <v>977259648</v>
+        <v>135590148</v>
       </c>
     </row>
     <row r="52">
@@ -2584,40 +2584,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>09633</t>
+          <t>02318</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>农夫山泉</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>46.42</v>
+        <v>62.95</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5</v>
+        <v>-0.75</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.07</v>
+        <v>-1.18</v>
       </c>
       <c r="G52" t="n">
-        <v>46.64</v>
+        <v>63.7</v>
       </c>
       <c r="H52" t="n">
-        <v>47</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>46.36</v>
+        <v>62.9</v>
       </c>
       <c r="J52" t="n">
-        <v>46.92</v>
+        <v>63.7</v>
       </c>
       <c r="K52" t="n">
-        <v>1830683</v>
+        <v>38718491</v>
       </c>
       <c r="L52" t="n">
-        <v>85349702</v>
+        <v>2459841280</v>
       </c>
     </row>
     <row r="53">
@@ -2626,40 +2626,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>00700</t>
+          <t>06185</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>腾讯控股</t>
+          <t>康希诺生物</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>473.4</v>
+        <v>29.48</v>
       </c>
       <c r="E53" t="n">
-        <v>-5.2</v>
+        <v>-0.36</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.09</v>
+        <v>-1.21</v>
       </c>
       <c r="G53" t="n">
-        <v>476</v>
+        <v>30</v>
       </c>
       <c r="H53" t="n">
-        <v>481.6</v>
+        <v>30</v>
       </c>
       <c r="I53" t="n">
-        <v>472.4</v>
+        <v>29.24</v>
       </c>
       <c r="J53" t="n">
-        <v>478.6</v>
+        <v>29.84</v>
       </c>
       <c r="K53" t="n">
-        <v>17623300</v>
+        <v>759400</v>
       </c>
       <c r="L53" t="n">
-        <v>8394160640</v>
+        <v>22363915</v>
       </c>
     </row>
     <row r="54">
@@ -2668,40 +2668,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>00998</t>
+          <t>00762</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>中信银行</t>
+          <t>中国联通</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>8.18</v>
+        <v>7.33</v>
       </c>
       <c r="E54" t="n">
         <v>-0.09</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.09</v>
+        <v>-1.21</v>
       </c>
       <c r="G54" t="n">
-        <v>8.27</v>
+        <v>7.4</v>
       </c>
       <c r="H54" t="n">
-        <v>8.289999999999999</v>
+        <v>7.45</v>
       </c>
       <c r="I54" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J54" t="n">
-        <v>8.27</v>
+        <v>7.42</v>
       </c>
       <c r="K54" t="n">
-        <v>26312111</v>
+        <v>14448950</v>
       </c>
       <c r="L54" t="n">
-        <v>215224453</v>
+        <v>106319584</v>
       </c>
     </row>
     <row r="55">
@@ -2710,40 +2710,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>06690</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>中远海控</t>
+          <t>海尔智家</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.34</v>
+        <v>21.92</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.17</v>
+        <v>-0.28</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.17</v>
+        <v>-1.26</v>
       </c>
       <c r="G55" t="n">
-        <v>14.51</v>
+        <v>21.92</v>
       </c>
       <c r="H55" t="n">
-        <v>14.59</v>
+        <v>22.32</v>
       </c>
       <c r="I55" t="n">
-        <v>14.32</v>
+        <v>21.92</v>
       </c>
       <c r="J55" t="n">
-        <v>14.51</v>
+        <v>22.2</v>
       </c>
       <c r="K55" t="n">
-        <v>7376919</v>
+        <v>18474062</v>
       </c>
       <c r="L55" t="n">
-        <v>106186860</v>
+        <v>409353872</v>
       </c>
     </row>
     <row r="56">
@@ -2752,40 +2752,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>02331</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>大唐发电</t>
+          <t>李宁</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2.49</v>
+        <v>20.18</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.03</v>
+        <v>-0.26</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.19</v>
+        <v>-1.27</v>
       </c>
       <c r="G56" t="n">
-        <v>2.53</v>
+        <v>20.38</v>
       </c>
       <c r="H56" t="n">
-        <v>2.54</v>
+        <v>20.74</v>
       </c>
       <c r="I56" t="n">
-        <v>2.46</v>
+        <v>20.14</v>
       </c>
       <c r="J56" t="n">
-        <v>2.52</v>
+        <v>20.44</v>
       </c>
       <c r="K56" t="n">
-        <v>16582000</v>
+        <v>19977839</v>
       </c>
       <c r="L56" t="n">
-        <v>41128360</v>
+        <v>408325488</v>
       </c>
     </row>
     <row r="57">
@@ -2794,40 +2794,40 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>00751</t>
+          <t>00941</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>创维集团</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6.17</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.08</v>
+        <v>-1.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
       <c r="G57" t="n">
-        <v>6.21</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>6.24</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>6.16</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>6.25</v>
+        <v>85.45</v>
       </c>
       <c r="K57" t="n">
-        <v>410000</v>
+        <v>19845402</v>
       </c>
       <c r="L57" t="n">
-        <v>2536340</v>
+        <v>1680936384</v>
       </c>
     </row>
     <row r="58">
@@ -2836,40 +2836,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>00780</t>
+          <t>03888</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>同程旅行</t>
+          <t>金山软件</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17.38</v>
+        <v>22.78</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.23</v>
+        <v>-0.3</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.31</v>
+        <v>-1.3</v>
       </c>
       <c r="G58" t="n">
-        <v>17.22</v>
+        <v>22.82</v>
       </c>
       <c r="H58" t="n">
-        <v>17.59</v>
+        <v>23.18</v>
       </c>
       <c r="I58" t="n">
-        <v>17.22</v>
+        <v>22.64</v>
       </c>
       <c r="J58" t="n">
-        <v>17.61</v>
+        <v>23.08</v>
       </c>
       <c r="K58" t="n">
-        <v>2434000</v>
+        <v>6571973</v>
       </c>
       <c r="L58" t="n">
-        <v>42331328</v>
+        <v>149956471</v>
       </c>
     </row>
     <row r="59">
@@ -2878,40 +2878,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>06618</t>
+          <t>02359</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>京东健康</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>44.52</v>
+        <v>136</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.33</v>
+        <v>-1.31</v>
       </c>
       <c r="G59" t="n">
-        <v>44.48</v>
+        <v>137.8</v>
       </c>
       <c r="H59" t="n">
-        <v>45.08</v>
+        <v>139.8</v>
       </c>
       <c r="I59" t="n">
-        <v>44.44</v>
+        <v>134</v>
       </c>
       <c r="J59" t="n">
-        <v>45.12</v>
+        <v>137.8</v>
       </c>
       <c r="K59" t="n">
-        <v>2728068</v>
+        <v>5183387</v>
       </c>
       <c r="L59" t="n">
-        <v>122161263</v>
+        <v>706065280</v>
       </c>
     </row>
     <row r="60">
@@ -2920,40 +2920,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01368</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>特步国际</t>
+          <t>中国电信</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4.35</v>
+        <v>5.2</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.36</v>
+        <v>-1.33</v>
       </c>
       <c r="G60" t="n">
-        <v>4.41</v>
+        <v>5.27</v>
       </c>
       <c r="H60" t="n">
-        <v>4.41</v>
+        <v>5.27</v>
       </c>
       <c r="I60" t="n">
-        <v>4.29</v>
+        <v>5.18</v>
       </c>
       <c r="J60" t="n">
-        <v>4.41</v>
+        <v>5.27</v>
       </c>
       <c r="K60" t="n">
-        <v>14971300</v>
+        <v>63285636</v>
       </c>
       <c r="L60" t="n">
-        <v>64862450</v>
+        <v>330407184</v>
       </c>
     </row>
     <row r="61">
@@ -2962,40 +2962,40 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>09618</t>
+          <t>03968</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>京东集团-SW</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>115.4</v>
+        <v>47.34</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.6</v>
+        <v>-0.64</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.37</v>
+        <v>-1.33</v>
       </c>
       <c r="G61" t="n">
-        <v>115.5</v>
+        <v>47.5</v>
       </c>
       <c r="H61" t="n">
-        <v>117.5</v>
+        <v>47.98</v>
       </c>
       <c r="I61" t="n">
-        <v>115.2</v>
+        <v>47.1</v>
       </c>
       <c r="J61" t="n">
-        <v>117</v>
+        <v>47.98</v>
       </c>
       <c r="K61" t="n">
-        <v>5504559</v>
+        <v>20940922</v>
       </c>
       <c r="L61" t="n">
-        <v>639289312</v>
+        <v>993069072</v>
       </c>
     </row>
     <row r="62">
@@ -3004,40 +3004,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>02013</t>
+          <t>00788</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>微盟集团</t>
+          <t>中国铁塔</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.44</v>
+        <v>11.07</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.37</v>
+        <v>-1.34</v>
       </c>
       <c r="G62" t="n">
-        <v>1.47</v>
+        <v>11.2</v>
       </c>
       <c r="H62" t="n">
-        <v>1.47</v>
+        <v>11.26</v>
       </c>
       <c r="I62" t="n">
-        <v>1.43</v>
+        <v>11.05</v>
       </c>
       <c r="J62" t="n">
-        <v>1.46</v>
+        <v>11.22</v>
       </c>
       <c r="K62" t="n">
-        <v>18295000</v>
+        <v>5485155</v>
       </c>
       <c r="L62" t="n">
-        <v>26414800</v>
+        <v>60942629</v>
       </c>
     </row>
     <row r="63">
@@ -3046,40 +3046,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>02318</t>
+          <t>03323</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>中国建材</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>60.05</v>
+        <v>5.09</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.85</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.4</v>
+        <v>-1.36</v>
       </c>
       <c r="G63" t="n">
-        <v>60.3</v>
+        <v>5.16</v>
       </c>
       <c r="H63" t="n">
-        <v>61.05</v>
+        <v>5.37</v>
       </c>
       <c r="I63" t="n">
-        <v>60.05</v>
+        <v>5.06</v>
       </c>
       <c r="J63" t="n">
-        <v>60.9</v>
+        <v>5.16</v>
       </c>
       <c r="K63" t="n">
-        <v>14526384</v>
+        <v>28086976</v>
       </c>
       <c r="L63" t="n">
-        <v>876620240</v>
+        <v>145267356</v>
       </c>
     </row>
     <row r="64">
@@ -3088,40 +3088,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01211</t>
+          <t>00027</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>比亚迪股份</t>
+          <t>银河娱乐</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>104.4</v>
+        <v>32.98</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.6</v>
+        <v>-0.46</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.51</v>
+        <v>-1.38</v>
       </c>
       <c r="G64" t="n">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="H64" t="n">
-        <v>107</v>
+        <v>33.16</v>
       </c>
       <c r="I64" t="n">
-        <v>103.8</v>
+        <v>32.68</v>
       </c>
       <c r="J64" t="n">
-        <v>106</v>
+        <v>33.44</v>
       </c>
       <c r="K64" t="n">
-        <v>13405332</v>
+        <v>9860197</v>
       </c>
       <c r="L64" t="n">
-        <v>1409462384</v>
+        <v>324256944</v>
       </c>
     </row>
     <row r="65">
@@ -3130,40 +3130,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>09888</t>
+          <t>01024</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>百度集团-SW</t>
+          <t>快手-W</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>123.8</v>
+        <v>42.92</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.9</v>
+        <v>-0.6</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.51</v>
+        <v>-1.38</v>
       </c>
       <c r="G65" t="n">
-        <v>125</v>
+        <v>42.68</v>
       </c>
       <c r="H65" t="n">
-        <v>126.9</v>
+        <v>43.22</v>
       </c>
       <c r="I65" t="n">
-        <v>123.7</v>
+        <v>42.48</v>
       </c>
       <c r="J65" t="n">
-        <v>125.7</v>
+        <v>43.52</v>
       </c>
       <c r="K65" t="n">
-        <v>4826734</v>
+        <v>20363688</v>
       </c>
       <c r="L65" t="n">
-        <v>603927680</v>
+        <v>871079664</v>
       </c>
     </row>
     <row r="66">
@@ -3172,40 +3172,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>03323</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>中国建材</t>
+          <t>农业银行</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.04</v>
+        <v>6.08</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.56</v>
+        <v>-1.46</v>
       </c>
       <c r="G66" t="n">
-        <v>5.18</v>
+        <v>6.17</v>
       </c>
       <c r="H66" t="n">
-        <v>5.18</v>
+        <v>6.3</v>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>6.06</v>
       </c>
       <c r="J66" t="n">
-        <v>5.12</v>
+        <v>6.17</v>
       </c>
       <c r="K66" t="n">
-        <v>13967665</v>
+        <v>184782475</v>
       </c>
       <c r="L66" t="n">
-        <v>70320481</v>
+        <v>1135962000</v>
       </c>
     </row>
     <row r="67">
@@ -3214,40 +3214,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>09922</t>
+          <t>01579</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>九毛九</t>
+          <t>颐海国际</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.79</v>
+        <v>16.41</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.03</v>
+        <v>-0.25</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.65</v>
+        <v>-1.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1.81</v>
+        <v>16.52</v>
       </c>
       <c r="H67" t="n">
-        <v>1.82</v>
+        <v>16.85</v>
       </c>
       <c r="I67" t="n">
-        <v>1.79</v>
+        <v>16.39</v>
       </c>
       <c r="J67" t="n">
-        <v>1.82</v>
+        <v>16.66</v>
       </c>
       <c r="K67" t="n">
-        <v>756000</v>
+        <v>1226000</v>
       </c>
       <c r="L67" t="n">
-        <v>1360695</v>
+        <v>20401843</v>
       </c>
     </row>
     <row r="68">
@@ -3256,40 +3256,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>03690</t>
+          <t>00992</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>美团-W</t>
+          <t>联想集团</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>80.40000000000001</v>
+        <v>11.68</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.45</v>
+        <v>-0.18</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.77</v>
+        <v>-1.52</v>
       </c>
       <c r="G68" t="n">
-        <v>80.84999999999999</v>
+        <v>11.78</v>
       </c>
       <c r="H68" t="n">
-        <v>81.65000000000001</v>
+        <v>11.89</v>
       </c>
       <c r="I68" t="n">
-        <v>80.25</v>
+        <v>11.53</v>
       </c>
       <c r="J68" t="n">
-        <v>81.84999999999999</v>
+        <v>11.86</v>
       </c>
       <c r="K68" t="n">
-        <v>20535870</v>
+        <v>75967543</v>
       </c>
       <c r="L68" t="n">
-        <v>1657374896</v>
+        <v>887051568</v>
       </c>
     </row>
     <row r="69">
@@ -3298,40 +3298,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>00175</t>
+          <t>01060</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>吉利汽车</t>
+          <t>大麦娱乐</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>21.98</v>
+        <v>0.57</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4</v>
+        <v>-0.01</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.79</v>
+        <v>-1.72</v>
       </c>
       <c r="G69" t="n">
-        <v>22.24</v>
+        <v>0.58</v>
       </c>
       <c r="H69" t="n">
-        <v>22.62</v>
+        <v>0.58</v>
       </c>
       <c r="I69" t="n">
-        <v>21.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>22.38</v>
+        <v>0.58</v>
       </c>
       <c r="K69" t="n">
-        <v>56133072</v>
+        <v>67131278</v>
       </c>
       <c r="L69" t="n">
-        <v>1231296816</v>
+        <v>38443964</v>
       </c>
     </row>
     <row r="70">
@@ -3340,40 +3340,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01772</t>
+          <t>02196</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>赣锋锂业</t>
+          <t>复星医药</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>78.45</v>
+        <v>19.22</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.55</v>
+        <v>-0.36</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.94</v>
+        <v>-1.84</v>
       </c>
       <c r="G70" t="n">
-        <v>81.3</v>
+        <v>19.58</v>
       </c>
       <c r="H70" t="n">
-        <v>82</v>
+        <v>19.58</v>
       </c>
       <c r="I70" t="n">
-        <v>77.55</v>
+        <v>19.03</v>
       </c>
       <c r="J70" t="n">
-        <v>80</v>
+        <v>19.58</v>
       </c>
       <c r="K70" t="n">
-        <v>4803980</v>
+        <v>2879735</v>
       </c>
       <c r="L70" t="n">
-        <v>379508896</v>
+        <v>55346491</v>
       </c>
     </row>
     <row r="71">
@@ -3382,40 +3382,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>03998</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>心动公司</t>
+          <t>波司登</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>63.65</v>
+        <v>4.26</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.3</v>
+        <v>-0.08</v>
       </c>
       <c r="F71" t="n">
-        <v>-2</v>
+        <v>-1.84</v>
       </c>
       <c r="G71" t="n">
-        <v>64.95</v>
+        <v>4.34</v>
       </c>
       <c r="H71" t="n">
-        <v>65.59999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="I71" t="n">
-        <v>63.5</v>
+        <v>4.25</v>
       </c>
       <c r="J71" t="n">
-        <v>64.95</v>
+        <v>4.34</v>
       </c>
       <c r="K71" t="n">
-        <v>1312600</v>
+        <v>11861106</v>
       </c>
       <c r="L71" t="n">
-        <v>84224440</v>
+        <v>50920875</v>
       </c>
     </row>
     <row r="72">
@@ -3424,40 +3424,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01896</t>
+          <t>00753</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>猫眼娱乐</t>
+          <t>中国国航</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5.73</v>
+        <v>4.67</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="F72" t="n">
-        <v>-2.05</v>
+        <v>-1.89</v>
       </c>
       <c r="G72" t="n">
-        <v>5.9</v>
+        <v>4.78</v>
       </c>
       <c r="H72" t="n">
-        <v>5.9</v>
+        <v>4.78</v>
       </c>
       <c r="I72" t="n">
-        <v>5.73</v>
+        <v>4.57</v>
       </c>
       <c r="J72" t="n">
-        <v>5.85</v>
+        <v>4.76</v>
       </c>
       <c r="K72" t="n">
-        <v>2138600</v>
+        <v>43981786</v>
       </c>
       <c r="L72" t="n">
-        <v>12361282</v>
+        <v>203743666</v>
       </c>
     </row>
     <row r="73">
@@ -3466,40 +3466,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>09866</t>
+          <t>00939</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>蔚来-SW</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>49.06</v>
+        <v>8.82</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.09</v>
+        <v>-0.17</v>
       </c>
       <c r="F73" t="n">
-        <v>-2.17</v>
+        <v>-1.89</v>
       </c>
       <c r="G73" t="n">
-        <v>49.44</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>50.15</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>49.04</v>
+        <v>8.73</v>
       </c>
       <c r="J73" t="n">
-        <v>50.15</v>
+        <v>8.99</v>
       </c>
       <c r="K73" t="n">
-        <v>2622111</v>
+        <v>352237536</v>
       </c>
       <c r="L73" t="n">
-        <v>129548727</v>
+        <v>3129836608</v>
       </c>
     </row>
     <row r="74">
@@ -3508,40 +3508,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>00868</t>
+          <t>00388</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>信义玻璃</t>
+          <t>香港交易所</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>9.710000000000001</v>
+        <v>411.6</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.22</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>-2.22</v>
+        <v>-1.95</v>
       </c>
       <c r="G74" t="n">
-        <v>9.91</v>
+        <v>422</v>
       </c>
       <c r="H74" t="n">
-        <v>10.03</v>
+        <v>427.8</v>
       </c>
       <c r="I74" t="n">
-        <v>9.640000000000001</v>
+        <v>411</v>
       </c>
       <c r="J74" t="n">
-        <v>9.93</v>
+        <v>419.8</v>
       </c>
       <c r="K74" t="n">
-        <v>9802174</v>
+        <v>5086174</v>
       </c>
       <c r="L74" t="n">
-        <v>96712571</v>
+        <v>2124384528</v>
       </c>
     </row>
     <row r="75">
@@ -3550,40 +3550,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>02020</t>
+          <t>02202</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>安踏体育</t>
+          <t>万科企业</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>81.40000000000001</v>
+        <v>2.98</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.85</v>
+        <v>-0.06</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.22</v>
+        <v>-1.97</v>
       </c>
       <c r="G75" t="n">
-        <v>83.5</v>
+        <v>3.04</v>
       </c>
       <c r="H75" t="n">
-        <v>83.7</v>
+        <v>3.05</v>
       </c>
       <c r="I75" t="n">
-        <v>81.34999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="J75" t="n">
-        <v>83.25</v>
+        <v>3.04</v>
       </c>
       <c r="K75" t="n">
-        <v>2476872</v>
+        <v>21283069</v>
       </c>
       <c r="L75" t="n">
-        <v>204261645</v>
+        <v>64025851</v>
       </c>
     </row>
     <row r="76">
@@ -3592,40 +3592,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01929</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>中远海控</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.78</v>
+        <v>14.39</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.25</v>
+        <v>-0.29</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.27</v>
+        <v>-1.98</v>
       </c>
       <c r="G76" t="n">
-        <v>10.98</v>
+        <v>14.52</v>
       </c>
       <c r="H76" t="n">
-        <v>11</v>
+        <v>14.52</v>
       </c>
       <c r="I76" t="n">
-        <v>10.77</v>
+        <v>14.21</v>
       </c>
       <c r="J76" t="n">
-        <v>11.03</v>
+        <v>14.68</v>
       </c>
       <c r="K76" t="n">
-        <v>3829150</v>
+        <v>18081918</v>
       </c>
       <c r="L76" t="n">
-        <v>41599845</v>
+        <v>259640552</v>
       </c>
     </row>
     <row r="77">
@@ -3634,40 +3634,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>00992</t>
+          <t>09698</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>联想集团</t>
+          <t>万国数据-SW</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.84</v>
+        <v>40.66</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.28</v>
+        <v>-0.82</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.31</v>
+        <v>-1.98</v>
       </c>
       <c r="G77" t="n">
-        <v>12.14</v>
+        <v>41</v>
       </c>
       <c r="H77" t="n">
-        <v>12.19</v>
+        <v>41.38</v>
       </c>
       <c r="I77" t="n">
-        <v>11.8</v>
+        <v>39.66</v>
       </c>
       <c r="J77" t="n">
-        <v>12.12</v>
+        <v>41.48</v>
       </c>
       <c r="K77" t="n">
-        <v>56554471</v>
+        <v>2891689</v>
       </c>
       <c r="L77" t="n">
-        <v>673565552</v>
+        <v>116410191</v>
       </c>
     </row>
     <row r="78">
@@ -3676,40 +3676,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>02319</t>
+          <t>01368</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>蒙牛乳业</t>
+          <t>特步国际</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>16.4</v>
+        <v>4.32</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.39</v>
+        <v>-0.09</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.32</v>
+        <v>-2.04</v>
       </c>
       <c r="G78" t="n">
-        <v>16.76</v>
+        <v>4.42</v>
       </c>
       <c r="H78" t="n">
-        <v>16.76</v>
+        <v>4.42</v>
       </c>
       <c r="I78" t="n">
-        <v>16.24</v>
+        <v>4.29</v>
       </c>
       <c r="J78" t="n">
-        <v>16.79</v>
+        <v>4.41</v>
       </c>
       <c r="K78" t="n">
-        <v>12279351</v>
+        <v>11702500</v>
       </c>
       <c r="L78" t="n">
-        <v>201534769</v>
+        <v>50666725</v>
       </c>
     </row>
     <row r="79">
@@ -3718,40 +3718,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>00027</t>
+          <t>00700</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>银河娱乐</t>
+          <t>腾讯控股</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>32.76</v>
+        <v>469.4</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.78</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.33</v>
+        <v>-2.05</v>
       </c>
       <c r="G79" t="n">
-        <v>33.54</v>
+        <v>474</v>
       </c>
       <c r="H79" t="n">
-        <v>33.54</v>
+        <v>474.8</v>
       </c>
       <c r="I79" t="n">
-        <v>32.74</v>
+        <v>463.2</v>
       </c>
       <c r="J79" t="n">
-        <v>33.54</v>
+        <v>479.2</v>
       </c>
       <c r="K79" t="n">
-        <v>15204729</v>
+        <v>31922294</v>
       </c>
       <c r="L79" t="n">
-        <v>504273072</v>
+        <v>14948681728</v>
       </c>
     </row>
     <row r="80">
@@ -3760,40 +3760,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>00909</t>
+          <t>00772</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>明源云</t>
+          <t>阅文集团</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2.09</v>
+        <v>24.64</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.05</v>
+        <v>-0.52</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.34</v>
+        <v>-2.07</v>
       </c>
       <c r="G80" t="n">
-        <v>2.14</v>
+        <v>24.9</v>
       </c>
       <c r="H80" t="n">
-        <v>2.14</v>
+        <v>25.14</v>
       </c>
       <c r="I80" t="n">
-        <v>2.08</v>
+        <v>24.38</v>
       </c>
       <c r="J80" t="n">
-        <v>2.14</v>
+        <v>25.16</v>
       </c>
       <c r="K80" t="n">
-        <v>3278298</v>
+        <v>2939483</v>
       </c>
       <c r="L80" t="n">
-        <v>6888139</v>
+        <v>72417052</v>
       </c>
     </row>
     <row r="81">
@@ -3802,40 +3802,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>02423</t>
+          <t>01357</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>贝壳-W</t>
+          <t>美图公司</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>40.62</v>
+        <v>4.19</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.98</v>
+        <v>-0.09</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.36</v>
+        <v>-2.1</v>
       </c>
       <c r="G81" t="n">
-        <v>42.16</v>
+        <v>4.24</v>
       </c>
       <c r="H81" t="n">
-        <v>42.2</v>
+        <v>4.26</v>
       </c>
       <c r="I81" t="n">
-        <v>40.58</v>
+        <v>4.17</v>
       </c>
       <c r="J81" t="n">
-        <v>41.6</v>
+        <v>4.28</v>
       </c>
       <c r="K81" t="n">
-        <v>7609100</v>
+        <v>23249004</v>
       </c>
       <c r="L81" t="n">
-        <v>313716912</v>
+        <v>97759429</v>
       </c>
     </row>
     <row r="82">
@@ -3844,40 +3844,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>09992</t>
+          <t>03988</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>泡泡玛特</t>
+          <t>中国银行</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>152.4</v>
+        <v>5.07</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.7</v>
+        <v>-0.11</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.37</v>
+        <v>-2.12</v>
       </c>
       <c r="G82" t="n">
-        <v>155</v>
+        <v>5.15</v>
       </c>
       <c r="H82" t="n">
-        <v>156.7</v>
+        <v>5.18</v>
       </c>
       <c r="I82" t="n">
-        <v>152</v>
+        <v>5.05</v>
       </c>
       <c r="J82" t="n">
-        <v>156.1</v>
+        <v>5.18</v>
       </c>
       <c r="K82" t="n">
-        <v>8548991</v>
+        <v>182953951</v>
       </c>
       <c r="L82" t="n">
-        <v>1312696464</v>
+        <v>933684224</v>
       </c>
     </row>
     <row r="83">
@@ -3886,40 +3886,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>00914</t>
+          <t>02018</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>海螺水泥</t>
+          <t>瑞声科技</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>19.68</v>
+        <v>35.98</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.48</v>
+        <v>-0.8</v>
       </c>
       <c r="F83" t="n">
-        <v>-2.38</v>
+        <v>-2.18</v>
       </c>
       <c r="G83" t="n">
-        <v>20.16</v>
+        <v>36.88</v>
       </c>
       <c r="H83" t="n">
-        <v>20.16</v>
+        <v>36.88</v>
       </c>
       <c r="I83" t="n">
-        <v>19.65</v>
+        <v>35.76</v>
       </c>
       <c r="J83" t="n">
-        <v>20.16</v>
+        <v>36.78</v>
       </c>
       <c r="K83" t="n">
-        <v>6608350</v>
+        <v>4794938</v>
       </c>
       <c r="L83" t="n">
-        <v>130715516</v>
+        <v>172662335</v>
       </c>
     </row>
     <row r="84">
@@ -3928,40 +3928,40 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>00241</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>阿里健康</t>
+          <t>心动公司</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4.44</v>
+        <v>62.7</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.11</v>
+        <v>-1.4</v>
       </c>
       <c r="F84" t="n">
-        <v>-2.42</v>
+        <v>-2.18</v>
       </c>
       <c r="G84" t="n">
-        <v>4.51</v>
+        <v>63.9</v>
       </c>
       <c r="H84" t="n">
-        <v>4.53</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>4.43</v>
+        <v>61.9</v>
       </c>
       <c r="J84" t="n">
-        <v>4.55</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>41545790</v>
+        <v>1702721</v>
       </c>
       <c r="L84" t="n">
-        <v>185638293</v>
+        <v>106699299</v>
       </c>
     </row>
     <row r="85">
@@ -3970,40 +3970,40 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01138</t>
+          <t>06969</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>中远海能</t>
+          <t>思摩尔国际</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>17.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.44</v>
+        <v>-0.21</v>
       </c>
       <c r="F85" t="n">
-        <v>-2.48</v>
+        <v>-2.21</v>
       </c>
       <c r="G85" t="n">
-        <v>18.04</v>
+        <v>9.5</v>
       </c>
       <c r="H85" t="n">
-        <v>18.06</v>
+        <v>9.5</v>
       </c>
       <c r="I85" t="n">
-        <v>16.62</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>17.73</v>
+        <v>9.5</v>
       </c>
       <c r="K85" t="n">
-        <v>21617739</v>
+        <v>5036405</v>
       </c>
       <c r="L85" t="n">
-        <v>369048112</v>
+        <v>47014979</v>
       </c>
     </row>
     <row r="86">
@@ -4012,40 +4012,40 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>02899</t>
+          <t>01398</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>工商银行</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>35.32</v>
+        <v>7.06</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.9</v>
+        <v>-0.16</v>
       </c>
       <c r="F86" t="n">
-        <v>-2.48</v>
+        <v>-2.22</v>
       </c>
       <c r="G86" t="n">
-        <v>35.88</v>
+        <v>7.13</v>
       </c>
       <c r="H86" t="n">
-        <v>35.88</v>
+        <v>7.23</v>
       </c>
       <c r="I86" t="n">
-        <v>35.18</v>
+        <v>7.01</v>
       </c>
       <c r="J86" t="n">
-        <v>36.22</v>
+        <v>7.22</v>
       </c>
       <c r="K86" t="n">
-        <v>26918823</v>
+        <v>375271984</v>
       </c>
       <c r="L86" t="n">
-        <v>954825680</v>
+        <v>2661316704</v>
       </c>
     </row>
     <row r="87">
@@ -4054,40 +4054,40 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>02150</t>
+          <t>00241</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>奈雪的茶</t>
+          <t>阿里健康</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.78</v>
+        <v>4.37</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="F87" t="n">
-        <v>-2.5</v>
+        <v>-2.24</v>
       </c>
       <c r="G87" t="n">
-        <v>0.79</v>
+        <v>4.45</v>
       </c>
       <c r="H87" t="n">
-        <v>0.8</v>
+        <v>4.45</v>
       </c>
       <c r="I87" t="n">
-        <v>0.78</v>
+        <v>4.36</v>
       </c>
       <c r="J87" t="n">
-        <v>0.8</v>
+        <v>4.47</v>
       </c>
       <c r="K87" t="n">
-        <v>2190500</v>
+        <v>66520762</v>
       </c>
       <c r="L87" t="n">
-        <v>1719527</v>
+        <v>292365456</v>
       </c>
     </row>
     <row r="88">
@@ -4096,40 +4096,40 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>09626</t>
+          <t>01929</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>哔哩哔哩-W</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>166.8</v>
+        <v>10.71</v>
       </c>
       <c r="E88" t="n">
-        <v>-4.4</v>
+        <v>-0.25</v>
       </c>
       <c r="F88" t="n">
-        <v>-2.57</v>
+        <v>-2.28</v>
       </c>
       <c r="G88" t="n">
-        <v>169.9</v>
+        <v>10.96</v>
       </c>
       <c r="H88" t="n">
-        <v>170.8</v>
+        <v>10.96</v>
       </c>
       <c r="I88" t="n">
-        <v>166.6</v>
+        <v>10.69</v>
       </c>
       <c r="J88" t="n">
-        <v>171.2</v>
+        <v>10.96</v>
       </c>
       <c r="K88" t="n">
-        <v>1629893</v>
+        <v>18913746</v>
       </c>
       <c r="L88" t="n">
-        <v>274619040</v>
+        <v>204279027</v>
       </c>
     </row>
     <row r="89">
@@ -4138,40 +4138,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>00268</t>
+          <t>00914</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>金蝶国际</t>
+          <t>海螺水泥</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>8.279999999999999</v>
+        <v>19.62</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.22</v>
+        <v>-0.46</v>
       </c>
       <c r="F89" t="n">
-        <v>-2.59</v>
+        <v>-2.29</v>
       </c>
       <c r="G89" t="n">
-        <v>8.35</v>
+        <v>19.74</v>
       </c>
       <c r="H89" t="n">
-        <v>8.43</v>
+        <v>19.83</v>
       </c>
       <c r="I89" t="n">
-        <v>8.17</v>
+        <v>19.51</v>
       </c>
       <c r="J89" t="n">
-        <v>8.5</v>
+        <v>20.08</v>
       </c>
       <c r="K89" t="n">
-        <v>21769800</v>
+        <v>8603113</v>
       </c>
       <c r="L89" t="n">
-        <v>179675925</v>
+        <v>168982867</v>
       </c>
     </row>
     <row r="90">
@@ -4180,40 +4180,40 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>06862</t>
+          <t>02020</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>海底捞</t>
+          <t>安踏体育</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.91</v>
+        <v>81.25</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.39</v>
+        <v>-1.95</v>
       </c>
       <c r="F90" t="n">
-        <v>-2.73</v>
+        <v>-2.34</v>
       </c>
       <c r="G90" t="n">
-        <v>14</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="H90" t="n">
-        <v>14.17</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>13.82</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>14.3</v>
+        <v>83.2</v>
       </c>
       <c r="K90" t="n">
-        <v>17328344</v>
+        <v>6634196</v>
       </c>
       <c r="L90" t="n">
-        <v>241436214</v>
+        <v>544240880</v>
       </c>
     </row>
     <row r="91">
@@ -4222,40 +4222,40 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>09988</t>
+          <t>02269</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>阿里巴巴-W</t>
+          <t>药明生物</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>126.6</v>
+        <v>33.14</v>
       </c>
       <c r="E91" t="n">
-        <v>-3.6</v>
+        <v>-0.8</v>
       </c>
       <c r="F91" t="n">
-        <v>-2.76</v>
+        <v>-2.36</v>
       </c>
       <c r="G91" t="n">
-        <v>128.8</v>
+        <v>33.62</v>
       </c>
       <c r="H91" t="n">
-        <v>130.6</v>
+        <v>33.82</v>
       </c>
       <c r="I91" t="n">
-        <v>126.3</v>
+        <v>32.8</v>
       </c>
       <c r="J91" t="n">
-        <v>130.2</v>
+        <v>33.94</v>
       </c>
       <c r="K91" t="n">
-        <v>49434010</v>
+        <v>28828739</v>
       </c>
       <c r="L91" t="n">
-        <v>6335634944</v>
+        <v>952763584</v>
       </c>
     </row>
     <row r="92">
@@ -4264,40 +4264,40 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>00981</t>
+          <t>02618</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>京东物流</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>66.34999999999999</v>
+        <v>15.06</v>
       </c>
       <c r="E92" t="n">
-        <v>-1.9</v>
+        <v>-0.37</v>
       </c>
       <c r="F92" t="n">
-        <v>-2.78</v>
+        <v>-2.4</v>
       </c>
       <c r="G92" t="n">
-        <v>68.7</v>
+        <v>15.42</v>
       </c>
       <c r="H92" t="n">
-        <v>68.90000000000001</v>
+        <v>15.42</v>
       </c>
       <c r="I92" t="n">
-        <v>66</v>
+        <v>15.05</v>
       </c>
       <c r="J92" t="n">
-        <v>68.25</v>
+        <v>15.43</v>
       </c>
       <c r="K92" t="n">
-        <v>69359841</v>
+        <v>6551731</v>
       </c>
       <c r="L92" t="n">
-        <v>4673491456</v>
+        <v>99372052</v>
       </c>
     </row>
     <row r="93">
@@ -4306,40 +4306,40 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01928</t>
+          <t>09868</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>金沙中国有限公司</t>
+          <t>小鹏集团-W</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>15.97</v>
+        <v>61</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.46</v>
+        <v>-1.5</v>
       </c>
       <c r="F93" t="n">
-        <v>-2.8</v>
+        <v>-2.4</v>
       </c>
       <c r="G93" t="n">
-        <v>16.45</v>
+        <v>61.7</v>
       </c>
       <c r="H93" t="n">
-        <v>16.45</v>
+        <v>62.5</v>
       </c>
       <c r="I93" t="n">
-        <v>15.93</v>
+        <v>60.85</v>
       </c>
       <c r="J93" t="n">
-        <v>16.43</v>
+        <v>62.5</v>
       </c>
       <c r="K93" t="n">
-        <v>12622744</v>
+        <v>9891880</v>
       </c>
       <c r="L93" t="n">
-        <v>203021150</v>
+        <v>607235296</v>
       </c>
     </row>
     <row r="94">
@@ -4348,40 +4348,40 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>09987</t>
+          <t>00780</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>百胜中国</t>
+          <t>同程旅行</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>369.6</v>
+        <v>17.75</v>
       </c>
       <c r="E94" t="n">
-        <v>-11.4</v>
+        <v>-0.46</v>
       </c>
       <c r="F94" t="n">
-        <v>-2.99</v>
+        <v>-2.53</v>
       </c>
       <c r="G94" t="n">
-        <v>379</v>
+        <v>17.97</v>
       </c>
       <c r="H94" t="n">
-        <v>379</v>
+        <v>18.2</v>
       </c>
       <c r="I94" t="n">
-        <v>368</v>
+        <v>17.59</v>
       </c>
       <c r="J94" t="n">
-        <v>381</v>
+        <v>18.21</v>
       </c>
       <c r="K94" t="n">
-        <v>433058</v>
+        <v>4421261</v>
       </c>
       <c r="L94" t="n">
-        <v>161434518</v>
+        <v>78337774</v>
       </c>
     </row>
     <row r="95">
@@ -4390,40 +4390,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>02600</t>
+          <t>02015</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>中国铝业</t>
+          <t>理想汽车-W</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.53</v>
+        <v>67.5</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.37</v>
+        <v>-1.75</v>
       </c>
       <c r="F95" t="n">
-        <v>-3.11</v>
+        <v>-2.53</v>
       </c>
       <c r="G95" t="n">
-        <v>11.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H95" t="n">
-        <v>11.7</v>
+        <v>69.75</v>
       </c>
       <c r="I95" t="n">
-        <v>11.42</v>
+        <v>67.3</v>
       </c>
       <c r="J95" t="n">
-        <v>11.9</v>
+        <v>69.25</v>
       </c>
       <c r="K95" t="n">
-        <v>20553326</v>
+        <v>7478198</v>
       </c>
       <c r="L95" t="n">
-        <v>237182157</v>
+        <v>509481504</v>
       </c>
     </row>
     <row r="96">
@@ -4432,40 +4432,40 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01179</t>
+          <t>09626</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>华住集团-S</t>
+          <t>哔哩哔哩-W</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>38.76</v>
+        <v>167.7</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.26</v>
+        <v>-4.5</v>
       </c>
       <c r="F96" t="n">
-        <v>-3.15</v>
+        <v>-2.61</v>
       </c>
       <c r="G96" t="n">
-        <v>39.4</v>
+        <v>168.6</v>
       </c>
       <c r="H96" t="n">
-        <v>39.4</v>
+        <v>169.4</v>
       </c>
       <c r="I96" t="n">
-        <v>38.34</v>
+        <v>166</v>
       </c>
       <c r="J96" t="n">
-        <v>40.02</v>
+        <v>172.2</v>
       </c>
       <c r="K96" t="n">
-        <v>2398453</v>
+        <v>1586083</v>
       </c>
       <c r="L96" t="n">
-        <v>93543754</v>
+        <v>266165196</v>
       </c>
     </row>
     <row r="97">
@@ -4474,40 +4474,40 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01810</t>
+          <t>06618</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>小米集团-W</t>
+          <t>京东健康</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>30.12</v>
+        <v>45.34</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.98</v>
+        <v>-1.22</v>
       </c>
       <c r="F97" t="n">
-        <v>-3.15</v>
+        <v>-2.62</v>
       </c>
       <c r="G97" t="n">
-        <v>31.1</v>
+        <v>45.66</v>
       </c>
       <c r="H97" t="n">
-        <v>31.2</v>
+        <v>46.46</v>
       </c>
       <c r="I97" t="n">
-        <v>30.1</v>
+        <v>45.04</v>
       </c>
       <c r="J97" t="n">
-        <v>31.1</v>
+        <v>46.56</v>
       </c>
       <c r="K97" t="n">
-        <v>133000222</v>
+        <v>5701218</v>
       </c>
       <c r="L97" t="n">
-        <v>4046856976</v>
+        <v>259633443</v>
       </c>
     </row>
     <row r="98">
@@ -4516,40 +4516,40 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01833</t>
+          <t>02333</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>平安好医生</t>
+          <t>长城汽车</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.65</v>
+        <v>11.54</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.36</v>
+        <v>-0.32</v>
       </c>
       <c r="F98" t="n">
-        <v>-3.27</v>
+        <v>-2.7</v>
       </c>
       <c r="G98" t="n">
-        <v>11.04</v>
+        <v>11.89</v>
       </c>
       <c r="H98" t="n">
-        <v>11.06</v>
+        <v>11.92</v>
       </c>
       <c r="I98" t="n">
-        <v>10.63</v>
+        <v>11.51</v>
       </c>
       <c r="J98" t="n">
-        <v>11.01</v>
+        <v>11.86</v>
       </c>
       <c r="K98" t="n">
-        <v>7716670</v>
+        <v>19030444</v>
       </c>
       <c r="L98" t="n">
-        <v>83086242</v>
+        <v>222263258</v>
       </c>
     </row>
     <row r="99">
@@ -4558,40 +4558,40 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>09868</t>
+          <t>03328</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>小鹏集团-W</t>
+          <t>交通银行</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>62.1</v>
+        <v>7.15</v>
       </c>
       <c r="E99" t="n">
-        <v>-2.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F99" t="n">
-        <v>-3.27</v>
+        <v>-2.72</v>
       </c>
       <c r="G99" t="n">
-        <v>64.45</v>
+        <v>7.39</v>
       </c>
       <c r="H99" t="n">
-        <v>64.90000000000001</v>
+        <v>7.39</v>
       </c>
       <c r="I99" t="n">
-        <v>62.1</v>
+        <v>7</v>
       </c>
       <c r="J99" t="n">
-        <v>64.2</v>
+        <v>7.35</v>
       </c>
       <c r="K99" t="n">
-        <v>8007746</v>
+        <v>65967229</v>
       </c>
       <c r="L99" t="n">
-        <v>507036336</v>
+        <v>472216096</v>
       </c>
     </row>
     <row r="100">
@@ -4600,40 +4600,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>03888</t>
+          <t>02899</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>金山软件</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>23.1</v>
+        <v>35.46</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="F100" t="n">
-        <v>-3.35</v>
+        <v>-2.74</v>
       </c>
       <c r="G100" t="n">
-        <v>23.32</v>
+        <v>35.9</v>
       </c>
       <c r="H100" t="n">
-        <v>23.58</v>
+        <v>36.18</v>
       </c>
       <c r="I100" t="n">
-        <v>23</v>
+        <v>35.22</v>
       </c>
       <c r="J100" t="n">
-        <v>23.9</v>
+        <v>36.46</v>
       </c>
       <c r="K100" t="n">
-        <v>7215821</v>
+        <v>36045031</v>
       </c>
       <c r="L100" t="n">
-        <v>167681463</v>
+        <v>1282534640</v>
       </c>
     </row>
     <row r="101">
@@ -4642,40 +4642,40 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>00772</t>
+          <t>01810</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>阅文集团</t>
+          <t>小米集团-W</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>24.44</v>
+        <v>29.26</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.86</v>
+        <v>-0.88</v>
       </c>
       <c r="F101" t="n">
-        <v>-3.4</v>
+        <v>-2.92</v>
       </c>
       <c r="G101" t="n">
-        <v>25.5</v>
+        <v>29.82</v>
       </c>
       <c r="H101" t="n">
-        <v>25.5</v>
+        <v>29.88</v>
       </c>
       <c r="I101" t="n">
-        <v>24.36</v>
+        <v>28.8</v>
       </c>
       <c r="J101" t="n">
-        <v>25.3</v>
+        <v>30.14</v>
       </c>
       <c r="K101" t="n">
-        <v>3966802</v>
+        <v>245776409</v>
       </c>
       <c r="L101" t="n">
-        <v>97885422</v>
+        <v>7165797632</v>
       </c>
     </row>
   </sheetData>

--- a/zhimingganggu.xlsx
+++ b/zhimingganggu.xlsx
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>71.05</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="F2" t="n">
-        <v>7.98</v>
+        <v>7.75</v>
       </c>
       <c r="G2" t="n">
         <v>66.34999999999999</v>
@@ -514,10 +514,10 @@
         <v>65.8</v>
       </c>
       <c r="K2" t="n">
-        <v>155499374</v>
+        <v>168177459</v>
       </c>
       <c r="L2" t="n">
-        <v>10768367360</v>
+        <v>11666287360</v>
       </c>
     </row>
     <row r="3">
@@ -547,7 +547,7 @@
         <v>0.98</v>
       </c>
       <c r="H3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="I3" t="n">
         <v>0.98</v>
@@ -556,10 +556,10 @@
         <v>0.98</v>
       </c>
       <c r="K3" t="n">
-        <v>8149000</v>
+        <v>10389000</v>
       </c>
       <c r="L3" t="n">
-        <v>8315599</v>
+        <v>10674919</v>
       </c>
     </row>
     <row r="4">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>114.6</v>
+        <v>114.1</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>6.01</v>
+        <v>5.55</v>
       </c>
       <c r="G4" t="n">
         <v>109</v>
@@ -598,10 +598,10 @@
         <v>108.1</v>
       </c>
       <c r="K4" t="n">
-        <v>58437352</v>
+        <v>61945445</v>
       </c>
       <c r="L4" t="n">
-        <v>6432826112</v>
+        <v>6832963072</v>
       </c>
     </row>
     <row r="5">
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66.3</v>
+        <v>66.45</v>
       </c>
       <c r="E5" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="F5" t="n">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="G5" t="n">
         <v>63.2</v>
@@ -640,10 +640,10 @@
         <v>63.25</v>
       </c>
       <c r="K5" t="n">
-        <v>16550110</v>
+        <v>17580160</v>
       </c>
       <c r="L5" t="n">
-        <v>1089991824</v>
+        <v>1158285664</v>
       </c>
     </row>
     <row r="6">
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.64</v>
+        <v>28.62</v>
       </c>
       <c r="E6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="F6" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="G6" t="n">
         <v>28.5</v>
@@ -682,10 +682,10 @@
         <v>27.4</v>
       </c>
       <c r="K6" t="n">
-        <v>88216758</v>
+        <v>102332708</v>
       </c>
       <c r="L6" t="n">
-        <v>2534612912</v>
+        <v>2938618224</v>
       </c>
     </row>
     <row r="7">
@@ -694,40 +694,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01918</t>
+          <t>02319</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>融创中国</t>
+          <t>蒙牛乳业</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.15</v>
+        <v>17.35</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04</v>
+        <v>0.65</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>3.89</v>
       </c>
       <c r="G7" t="n">
-        <v>1.11</v>
+        <v>16.95</v>
       </c>
       <c r="H7" t="n">
-        <v>1.17</v>
+        <v>17.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>16.76</v>
       </c>
       <c r="J7" t="n">
-        <v>1.11</v>
+        <v>16.7</v>
       </c>
       <c r="K7" t="n">
-        <v>270440528</v>
+        <v>35319383</v>
       </c>
       <c r="L7" t="n">
-        <v>308209472</v>
+        <v>608823248</v>
       </c>
     </row>
     <row r="8">
@@ -736,40 +736,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>02319</t>
+          <t>01918</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>蒙牛乳业</t>
+          <t>融创中国</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.26</v>
+        <v>1.15</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F8" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>16.95</v>
+        <v>1.11</v>
       </c>
       <c r="H8" t="n">
-        <v>17.5</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>16.76</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>16.7</v>
+        <v>1.11</v>
       </c>
       <c r="K8" t="n">
-        <v>30114827</v>
+        <v>279653536</v>
       </c>
       <c r="L8" t="n">
-        <v>518692320</v>
+        <v>318791712</v>
       </c>
     </row>
     <row r="9">
@@ -778,40 +778,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>00175</t>
+          <t>00291</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>吉利汽车</t>
+          <t>华润啤酒</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.9</v>
+        <v>26.84</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="F9" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="G9" t="n">
-        <v>22.88</v>
+        <v>26.16</v>
       </c>
       <c r="H9" t="n">
-        <v>23.3</v>
+        <v>26.96</v>
       </c>
       <c r="I9" t="n">
-        <v>22.08</v>
+        <v>26.06</v>
       </c>
       <c r="J9" t="n">
-        <v>22.34</v>
+        <v>26.18</v>
       </c>
       <c r="K9" t="n">
-        <v>82040697</v>
+        <v>24196025</v>
       </c>
       <c r="L9" t="n">
-        <v>1863163440</v>
+        <v>643676256</v>
       </c>
     </row>
     <row r="10">
@@ -820,40 +820,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09999</t>
+          <t>00175</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>网易-S</t>
+          <t>吉利汽车</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>179.2</v>
+        <v>22.9</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="G10" t="n">
-        <v>178.1</v>
+        <v>22.88</v>
       </c>
       <c r="H10" t="n">
-        <v>180.3</v>
+        <v>23.3</v>
       </c>
       <c r="I10" t="n">
-        <v>177.7</v>
+        <v>22.08</v>
       </c>
       <c r="J10" t="n">
-        <v>175</v>
+        <v>22.34</v>
       </c>
       <c r="K10" t="n">
-        <v>8736682</v>
+        <v>99101192</v>
       </c>
       <c r="L10" t="n">
-        <v>1560520496</v>
+        <v>2253862560</v>
       </c>
     </row>
     <row r="11">
@@ -862,40 +862,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>00291</t>
+          <t>09999</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>华润啤酒</t>
+          <t>网易-S</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>26.8</v>
+        <v>179</v>
       </c>
       <c r="E11" t="n">
-        <v>0.62</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="G11" t="n">
-        <v>26.16</v>
+        <v>178.1</v>
       </c>
       <c r="H11" t="n">
-        <v>26.96</v>
+        <v>180.3</v>
       </c>
       <c r="I11" t="n">
-        <v>26.06</v>
+        <v>177.7</v>
       </c>
       <c r="J11" t="n">
-        <v>26.18</v>
+        <v>175</v>
       </c>
       <c r="K11" t="n">
-        <v>20272525</v>
+        <v>11256682</v>
       </c>
       <c r="L11" t="n">
-        <v>538421680</v>
+        <v>2011672208</v>
       </c>
     </row>
     <row r="12">
@@ -904,40 +904,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>00873</t>
+          <t>02007</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>世茂服务</t>
+          <t>碧桂园</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.29</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="G12" t="n">
-        <v>0.59</v>
+        <v>0.285</v>
       </c>
       <c r="H12" t="n">
-        <v>0.63</v>
+        <v>0.295</v>
       </c>
       <c r="I12" t="n">
-        <v>0.59</v>
+        <v>0.28</v>
       </c>
       <c r="J12" t="n">
-        <v>0.59</v>
+        <v>0.285</v>
       </c>
       <c r="K12" t="n">
-        <v>1353000</v>
+        <v>276181232</v>
       </c>
       <c r="L12" t="n">
-        <v>819630</v>
+        <v>79516259</v>
       </c>
     </row>
     <row r="13">
@@ -946,40 +946,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>00268</t>
+          <t>00873</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>金蝶国际</t>
+          <t>世茂服务</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8.529999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="F13" t="n">
-        <v>1.07</v>
+        <v>1.69</v>
       </c>
       <c r="G13" t="n">
-        <v>8.390000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H13" t="n">
-        <v>8.58</v>
+        <v>0.63</v>
       </c>
       <c r="I13" t="n">
-        <v>8.289999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="J13" t="n">
-        <v>8.44</v>
+        <v>0.59</v>
       </c>
       <c r="K13" t="n">
-        <v>33873920</v>
+        <v>1510000</v>
       </c>
       <c r="L13" t="n">
-        <v>287360144</v>
+        <v>916470</v>
       </c>
     </row>
     <row r="14">
@@ -988,40 +988,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>00763</t>
+          <t>00268</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中兴通讯</t>
+          <t>金蝶国际</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24.94</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
-        <v>24.7</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>25.2</v>
+        <v>8.58</v>
       </c>
       <c r="I14" t="n">
-        <v>24.22</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>24.74</v>
+        <v>8.44</v>
       </c>
       <c r="K14" t="n">
-        <v>17083488</v>
+        <v>39284920</v>
       </c>
       <c r="L14" t="n">
-        <v>421246224</v>
+        <v>333510768</v>
       </c>
     </row>
     <row r="15">
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F15" t="n">
-        <v>0.58</v>
+        <v>1.16</v>
       </c>
       <c r="G15" t="n">
         <v>3.43</v>
@@ -1060,10 +1060,10 @@
         <v>3.44</v>
       </c>
       <c r="K15" t="n">
-        <v>57691000</v>
+        <v>94287350</v>
       </c>
       <c r="L15" t="n">
-        <v>200077537</v>
+        <v>327344832</v>
       </c>
     </row>
     <row r="16">
@@ -1072,40 +1072,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09992</t>
+          <t>00763</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>泡泡玛特</t>
+          <t>中兴通讯</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>157.6</v>
+        <v>24.94</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>0.51</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>155.9</v>
+        <v>24.7</v>
       </c>
       <c r="H16" t="n">
-        <v>159.5</v>
+        <v>25.2</v>
       </c>
       <c r="I16" t="n">
-        <v>154.3</v>
+        <v>24.22</v>
       </c>
       <c r="J16" t="n">
-        <v>156.8</v>
+        <v>24.74</v>
       </c>
       <c r="K16" t="n">
-        <v>11642684</v>
+        <v>18542688</v>
       </c>
       <c r="L16" t="n">
-        <v>1823918416</v>
+        <v>457668000</v>
       </c>
     </row>
     <row r="17">
@@ -1114,40 +1114,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09961</t>
+          <t>01093</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>携程集团-S</t>
+          <t>石药集团</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>419.2</v>
+        <v>8.41</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>0.05</v>
       </c>
       <c r="F17" t="n">
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="G17" t="n">
-        <v>415.2</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>419.6</v>
+        <v>8.44</v>
       </c>
       <c r="I17" t="n">
-        <v>414.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>417.2</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>1311444</v>
+        <v>94312015</v>
       </c>
       <c r="L17" t="n">
-        <v>547657088</v>
+        <v>785529120</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>02423</t>
+          <t>09987</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>贝壳-W</t>
+          <t>百胜中国</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.32</v>
+        <v>381</v>
       </c>
       <c r="E18" t="n">
-        <v>0.16</v>
+        <v>1.8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="G18" t="n">
-        <v>42.04</v>
+        <v>383</v>
       </c>
       <c r="H18" t="n">
-        <v>43.32</v>
+        <v>392</v>
       </c>
       <c r="I18" t="n">
-        <v>41.46</v>
+        <v>377.2</v>
       </c>
       <c r="J18" t="n">
-        <v>42.16</v>
+        <v>379.2</v>
       </c>
       <c r="K18" t="n">
-        <v>10005400</v>
+        <v>1023859</v>
       </c>
       <c r="L18" t="n">
-        <v>427832896</v>
+        <v>391039632</v>
       </c>
     </row>
     <row r="19">
@@ -1198,40 +1198,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09987</t>
+          <t>02423</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>百胜中国</t>
+          <t>贝壳-W</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>380.6</v>
+        <v>42.32</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4</v>
+        <v>0.16</v>
       </c>
       <c r="F19" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="G19" t="n">
-        <v>383</v>
+        <v>42.04</v>
       </c>
       <c r="H19" t="n">
-        <v>392</v>
+        <v>43.32</v>
       </c>
       <c r="I19" t="n">
-        <v>377.2</v>
+        <v>41.46</v>
       </c>
       <c r="J19" t="n">
-        <v>379.2</v>
+        <v>42.16</v>
       </c>
       <c r="K19" t="n">
-        <v>742209</v>
+        <v>12236700</v>
       </c>
       <c r="L19" t="n">
-        <v>283798688</v>
+        <v>522234944</v>
       </c>
     </row>
     <row r="20">
@@ -1240,40 +1240,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>03690</t>
+          <t>09992</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>美团-W</t>
+          <t>泡泡玛特</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>83.45</v>
+        <v>157.2</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F20" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="G20" t="n">
-        <v>81.90000000000001</v>
+        <v>155.9</v>
       </c>
       <c r="H20" t="n">
-        <v>84.5</v>
+        <v>159.5</v>
       </c>
       <c r="I20" t="n">
-        <v>81.25</v>
+        <v>154.3</v>
       </c>
       <c r="J20" t="n">
-        <v>83.15000000000001</v>
+        <v>156.8</v>
       </c>
       <c r="K20" t="n">
-        <v>38275724</v>
+        <v>13723473</v>
       </c>
       <c r="L20" t="n">
-        <v>3174579760</v>
+        <v>2151348304</v>
       </c>
     </row>
     <row r="21">
@@ -1282,40 +1282,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01093</t>
+          <t>09961</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>石药集团</t>
+          <t>携程集团-S</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8.390000000000001</v>
+        <v>417.8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
       <c r="F21" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
       <c r="G21" t="n">
-        <v>8.289999999999999</v>
+        <v>415.2</v>
       </c>
       <c r="H21" t="n">
-        <v>8.44</v>
+        <v>419.6</v>
       </c>
       <c r="I21" t="n">
-        <v>8.199999999999999</v>
+        <v>414.4</v>
       </c>
       <c r="J21" t="n">
-        <v>8.359999999999999</v>
+        <v>417.2</v>
       </c>
       <c r="K21" t="n">
-        <v>78219716</v>
+        <v>1993044</v>
       </c>
       <c r="L21" t="n">
-        <v>650579328</v>
+        <v>832539488</v>
       </c>
     </row>
     <row r="22">
@@ -1324,40 +1324,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>02007</t>
+          <t>03690</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>碧桂园</t>
+          <t>美团-W</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.285</v>
+        <v>83.25</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="G22" t="n">
-        <v>0.285</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.295</v>
+        <v>84.5</v>
       </c>
       <c r="I22" t="n">
-        <v>0.28</v>
+        <v>81.25</v>
       </c>
       <c r="J22" t="n">
-        <v>0.285</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>263479228</v>
+        <v>45918845</v>
       </c>
       <c r="L22" t="n">
-        <v>75855644</v>
+        <v>3811345616</v>
       </c>
     </row>
     <row r="23">
@@ -1366,40 +1366,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>00656</t>
+          <t>01299</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>复星国际</t>
+          <t>友邦保险</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4.12</v>
+        <v>85.05</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="G23" t="n">
-        <v>4.1</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>4.16</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>4.05</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>4.12</v>
+        <v>84.95</v>
       </c>
       <c r="K23" t="n">
-        <v>10344364</v>
+        <v>36086904</v>
       </c>
       <c r="L23" t="n">
-        <v>42437499</v>
+        <v>3083552752</v>
       </c>
     </row>
     <row r="24">
@@ -1408,16 +1408,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>00520</t>
+          <t>06862</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>呷哺呷哺</t>
+          <t>海底捞</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.41</v>
+        <v>14.36</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1426,22 +1426,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.415</v>
+        <v>14.36</v>
       </c>
       <c r="H24" t="n">
-        <v>0.425</v>
+        <v>14.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0.41</v>
+        <v>14.28</v>
       </c>
       <c r="J24" t="n">
-        <v>0.41</v>
+        <v>14.36</v>
       </c>
       <c r="K24" t="n">
-        <v>4046500</v>
+        <v>9281975</v>
       </c>
       <c r="L24" t="n">
-        <v>1674637</v>
+        <v>133346407</v>
       </c>
     </row>
     <row r="25">
@@ -1450,40 +1450,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01299</t>
+          <t>01060</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>友邦保险</t>
+          <t>大麦娱乐</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>84.84999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>86.59999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="H25" t="n">
-        <v>87.15000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="I25" t="n">
-        <v>84.40000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>84.95</v>
+        <v>0.58</v>
       </c>
       <c r="K25" t="n">
-        <v>25042541</v>
+        <v>74671278</v>
       </c>
       <c r="L25" t="n">
-        <v>2144556144</v>
+        <v>42815764</v>
       </c>
     </row>
     <row r="26">
@@ -1492,40 +1492,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>00751</t>
+          <t>00883</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>创维集团</t>
+          <t>中国海洋石油</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6.25</v>
+        <v>29.38</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>6.21</v>
+        <v>29.6</v>
       </c>
       <c r="H26" t="n">
-        <v>6.26</v>
+        <v>29.8</v>
       </c>
       <c r="I26" t="n">
-        <v>6.21</v>
+        <v>29.08</v>
       </c>
       <c r="J26" t="n">
-        <v>6.26</v>
+        <v>29.38</v>
       </c>
       <c r="K26" t="n">
-        <v>540110</v>
+        <v>97951658</v>
       </c>
       <c r="L26" t="n">
-        <v>3368599</v>
+        <v>2878468256</v>
       </c>
     </row>
     <row r="27">
@@ -1534,40 +1534,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01772</t>
+          <t>00751</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>赣锋锂业</t>
+          <t>创维集团</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>83.8</v>
+        <v>6.26</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>84.2</v>
+        <v>6.21</v>
       </c>
       <c r="H27" t="n">
-        <v>87.34999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="I27" t="n">
-        <v>82.5</v>
+        <v>6.21</v>
       </c>
       <c r="J27" t="n">
-        <v>83.95</v>
+        <v>6.26</v>
       </c>
       <c r="K27" t="n">
-        <v>14093676</v>
+        <v>842110</v>
       </c>
       <c r="L27" t="n">
-        <v>1193971168</v>
+        <v>5257199</v>
       </c>
     </row>
     <row r="28">
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>53.9</v>
+        <v>53.95</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.19</v>
+        <v>-0.09</v>
       </c>
       <c r="G28" t="n">
         <v>53.35</v>
@@ -1606,10 +1606,10 @@
         <v>54</v>
       </c>
       <c r="K28" t="n">
-        <v>3332698</v>
+        <v>4035266</v>
       </c>
       <c r="L28" t="n">
-        <v>179334798</v>
+        <v>217170553</v>
       </c>
     </row>
     <row r="29">
@@ -1618,40 +1618,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>00285</t>
+          <t>01928</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>比亚迪电子</t>
+          <t>金沙中国有限公司</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>26.54</v>
+        <v>16.32</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.23</v>
+        <v>-0.12</v>
       </c>
       <c r="G29" t="n">
-        <v>26.42</v>
+        <v>16.24</v>
       </c>
       <c r="H29" t="n">
-        <v>26.88</v>
+        <v>16.33</v>
       </c>
       <c r="I29" t="n">
-        <v>26.12</v>
+        <v>15.96</v>
       </c>
       <c r="J29" t="n">
-        <v>26.6</v>
+        <v>16.34</v>
       </c>
       <c r="K29" t="n">
-        <v>8655279</v>
+        <v>11293939</v>
       </c>
       <c r="L29" t="n">
-        <v>229675835</v>
+        <v>182660824</v>
       </c>
     </row>
     <row r="30">
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>39.98</v>
+        <v>40</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="G30" t="n">
         <v>40.1</v>
@@ -1684,16 +1684,16 @@
         <v>40.7</v>
       </c>
       <c r="I30" t="n">
-        <v>39.94</v>
+        <v>39.92</v>
       </c>
       <c r="J30" t="n">
         <v>40.08</v>
       </c>
       <c r="K30" t="n">
-        <v>1712750</v>
+        <v>2238750</v>
       </c>
       <c r="L30" t="n">
-        <v>68880204</v>
+        <v>89920199</v>
       </c>
     </row>
     <row r="31">
@@ -1702,40 +1702,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>06862</t>
+          <t>02382</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>海底捞</t>
+          <t>舜宇光学科技</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.32</v>
+        <v>63.7</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.28</v>
+        <v>-0.23</v>
       </c>
       <c r="G31" t="n">
-        <v>14.36</v>
+        <v>63</v>
       </c>
       <c r="H31" t="n">
-        <v>14.5</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>14.29</v>
+        <v>62.6</v>
       </c>
       <c r="J31" t="n">
-        <v>14.36</v>
+        <v>63.85</v>
       </c>
       <c r="K31" t="n">
-        <v>7411975</v>
+        <v>10397594</v>
       </c>
       <c r="L31" t="n">
-        <v>106543785</v>
+        <v>659479840</v>
       </c>
     </row>
     <row r="32">
@@ -1744,40 +1744,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01876</t>
+          <t>00656</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>百威亚太</t>
+          <t>复星国际</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7.68</v>
+        <v>4.11</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.39</v>
+        <v>-0.24</v>
       </c>
       <c r="G32" t="n">
-        <v>7.66</v>
+        <v>4.1</v>
       </c>
       <c r="H32" t="n">
-        <v>7.72</v>
+        <v>4.16</v>
       </c>
       <c r="I32" t="n">
-        <v>7.54</v>
+        <v>4.05</v>
       </c>
       <c r="J32" t="n">
-        <v>7.71</v>
+        <v>4.12</v>
       </c>
       <c r="K32" t="n">
-        <v>10281900</v>
+        <v>12134728</v>
       </c>
       <c r="L32" t="n">
-        <v>78454907</v>
+        <v>49806395</v>
       </c>
     </row>
     <row r="33">
@@ -1786,40 +1786,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02382</t>
+          <t>00909</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>舜宇光学科技</t>
+          <t>明源云</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>63.6</v>
+        <v>2.1</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.25</v>
+        <v>-0.01</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="G33" t="n">
-        <v>63</v>
+        <v>2.12</v>
       </c>
       <c r="H33" t="n">
-        <v>64.15000000000001</v>
+        <v>2.12</v>
       </c>
       <c r="I33" t="n">
-        <v>62.6</v>
+        <v>2.09</v>
       </c>
       <c r="J33" t="n">
-        <v>63.85</v>
+        <v>2.11</v>
       </c>
       <c r="K33" t="n">
-        <v>7941894</v>
+        <v>2969000</v>
       </c>
       <c r="L33" t="n">
-        <v>503184128</v>
+        <v>6232804</v>
       </c>
     </row>
     <row r="34">
@@ -1828,40 +1828,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>00909</t>
+          <t>01896</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>明源云</t>
+          <t>猫眼娱乐</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.1</v>
+        <v>5.96</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.47</v>
+        <v>-0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>2.12</v>
+        <v>5.99</v>
       </c>
       <c r="H34" t="n">
-        <v>2.12</v>
+        <v>6.02</v>
       </c>
       <c r="I34" t="n">
-        <v>2.09</v>
+        <v>5.89</v>
       </c>
       <c r="J34" t="n">
-        <v>2.11</v>
+        <v>5.99</v>
       </c>
       <c r="K34" t="n">
-        <v>2558000</v>
+        <v>28184000</v>
       </c>
       <c r="L34" t="n">
-        <v>5371084</v>
+        <v>159936022</v>
       </c>
     </row>
     <row r="35">
@@ -1870,40 +1870,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>00883</t>
+          <t>00020</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>中国海洋石油</t>
+          <t>商汤-W</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29.24</v>
+        <v>1.98</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.48</v>
+        <v>-0.5</v>
       </c>
       <c r="G35" t="n">
-        <v>29.6</v>
+        <v>1.97</v>
       </c>
       <c r="H35" t="n">
-        <v>29.8</v>
+        <v>1.99</v>
       </c>
       <c r="I35" t="n">
-        <v>29.08</v>
+        <v>1.93</v>
       </c>
       <c r="J35" t="n">
-        <v>29.38</v>
+        <v>1.99</v>
       </c>
       <c r="K35" t="n">
-        <v>90890158</v>
+        <v>370436240</v>
       </c>
       <c r="L35" t="n">
-        <v>2671668848</v>
+        <v>728007376</v>
       </c>
     </row>
     <row r="36">
@@ -1912,40 +1912,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>00998</t>
+          <t>06049</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>中信银行</t>
+          <t>保利物业</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.220000000000001</v>
+        <v>31.26</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.48</v>
+        <v>-0.51</v>
       </c>
       <c r="G36" t="n">
-        <v>8.34</v>
+        <v>31.48</v>
       </c>
       <c r="H36" t="n">
-        <v>8.4</v>
+        <v>31.66</v>
       </c>
       <c r="I36" t="n">
-        <v>8.06</v>
+        <v>31.1</v>
       </c>
       <c r="J36" t="n">
-        <v>8.26</v>
+        <v>31.42</v>
       </c>
       <c r="K36" t="n">
-        <v>53891018</v>
+        <v>703400</v>
       </c>
       <c r="L36" t="n">
-        <v>442009552</v>
+        <v>22012885</v>
       </c>
     </row>
     <row r="37">
@@ -1954,40 +1954,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01896</t>
+          <t>01876</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>猫眼娱乐</t>
+          <t>百威亚太</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5.96</v>
+        <v>7.67</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5</v>
+        <v>-0.52</v>
       </c>
       <c r="G37" t="n">
-        <v>5.99</v>
+        <v>7.66</v>
       </c>
       <c r="H37" t="n">
-        <v>6.02</v>
+        <v>7.72</v>
       </c>
       <c r="I37" t="n">
-        <v>5.89</v>
+        <v>7.54</v>
       </c>
       <c r="J37" t="n">
-        <v>5.99</v>
+        <v>7.71</v>
       </c>
       <c r="K37" t="n">
-        <v>27944600</v>
+        <v>12429600</v>
       </c>
       <c r="L37" t="n">
-        <v>158509709</v>
+        <v>94921179</v>
       </c>
     </row>
     <row r="38">
@@ -1996,40 +1996,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>00020</t>
+          <t>00285</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>商汤-W</t>
+          <t>比亚迪电子</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.98</v>
+        <v>26.46</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.01</v>
+        <v>-0.14</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5</v>
+        <v>-0.53</v>
       </c>
       <c r="G38" t="n">
-        <v>1.97</v>
+        <v>26.42</v>
       </c>
       <c r="H38" t="n">
-        <v>1.99</v>
+        <v>26.88</v>
       </c>
       <c r="I38" t="n">
-        <v>1.93</v>
+        <v>26.12</v>
       </c>
       <c r="J38" t="n">
-        <v>1.99</v>
+        <v>26.6</v>
       </c>
       <c r="K38" t="n">
-        <v>321491008</v>
+        <v>10650779</v>
       </c>
       <c r="L38" t="n">
-        <v>631012480</v>
+        <v>282383920</v>
       </c>
     </row>
     <row r="39">
@@ -2038,40 +2038,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01928</t>
+          <t>00005</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>金沙中国有限公司</t>
+          <t>汇丰控股</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16.25</v>
+        <v>140.2</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.09</v>
+        <v>-0.8</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.55</v>
+        <v>-0.57</v>
       </c>
       <c r="G39" t="n">
-        <v>16.24</v>
+        <v>139.8</v>
       </c>
       <c r="H39" t="n">
-        <v>16.29</v>
+        <v>141.1</v>
       </c>
       <c r="I39" t="n">
-        <v>15.96</v>
+        <v>139.1</v>
       </c>
       <c r="J39" t="n">
-        <v>16.34</v>
+        <v>141</v>
       </c>
       <c r="K39" t="n">
-        <v>7338824</v>
+        <v>18699023</v>
       </c>
       <c r="L39" t="n">
-        <v>118167476</v>
+        <v>2622051968</v>
       </c>
     </row>
     <row r="40">
@@ -2080,40 +2080,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>06186</t>
+          <t>02013</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>中国飞鹤</t>
+          <t>微盟集团</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.49</v>
+        <v>1.46</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.57</v>
+        <v>-0.68</v>
       </c>
       <c r="G40" t="n">
-        <v>3.51</v>
+        <v>1.47</v>
       </c>
       <c r="H40" t="n">
-        <v>3.51</v>
+        <v>1.47</v>
       </c>
       <c r="I40" t="n">
-        <v>3.48</v>
+        <v>1.44</v>
       </c>
       <c r="J40" t="n">
-        <v>3.51</v>
+        <v>1.47</v>
       </c>
       <c r="K40" t="n">
-        <v>7009800</v>
+        <v>20441000</v>
       </c>
       <c r="L40" t="n">
-        <v>24481675</v>
+        <v>29778334</v>
       </c>
     </row>
     <row r="41">
@@ -2122,40 +2122,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>09888</t>
+          <t>00998</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>百度集团-SW</t>
+          <t>中信银行</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>119.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.7</v>
+        <v>-0.06</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.58</v>
+        <v>-0.73</v>
       </c>
       <c r="G41" t="n">
-        <v>118.6</v>
+        <v>8.34</v>
       </c>
       <c r="H41" t="n">
-        <v>119.8</v>
+        <v>8.4</v>
       </c>
       <c r="I41" t="n">
-        <v>117</v>
+        <v>8.06</v>
       </c>
       <c r="J41" t="n">
-        <v>119.9</v>
+        <v>8.26</v>
       </c>
       <c r="K41" t="n">
-        <v>6899370</v>
+        <v>60773208</v>
       </c>
       <c r="L41" t="n">
-        <v>816262944</v>
+        <v>498475472</v>
       </c>
     </row>
     <row r="42">
@@ -2164,40 +2164,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>03900</t>
+          <t>01772</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>绿城中国</t>
+          <t>赣锋锂业</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9.66</v>
+        <v>83.3</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.06</v>
+        <v>-0.65</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.62</v>
+        <v>-0.77</v>
       </c>
       <c r="G42" t="n">
-        <v>9.720000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="H42" t="n">
-        <v>9.94</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>9.65</v>
+        <v>82.5</v>
       </c>
       <c r="J42" t="n">
-        <v>9.720000000000001</v>
+        <v>83.95</v>
       </c>
       <c r="K42" t="n">
-        <v>9379227</v>
+        <v>16706349</v>
       </c>
       <c r="L42" t="n">
-        <v>91640177</v>
+        <v>1412375184</v>
       </c>
     </row>
     <row r="43">
@@ -2206,40 +2206,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01458</t>
+          <t>06098</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>周黑鸭</t>
+          <t>碧桂园服务</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.5</v>
+        <v>6.22</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.66</v>
+        <v>-0.8</v>
       </c>
       <c r="G43" t="n">
-        <v>1.49</v>
+        <v>6.25</v>
       </c>
       <c r="H43" t="n">
-        <v>1.51</v>
+        <v>6.29</v>
       </c>
       <c r="I43" t="n">
-        <v>1.47</v>
+        <v>6.2</v>
       </c>
       <c r="J43" t="n">
-        <v>1.51</v>
+        <v>6.27</v>
       </c>
       <c r="K43" t="n">
-        <v>2166500</v>
+        <v>3181120</v>
       </c>
       <c r="L43" t="n">
-        <v>3226155</v>
+        <v>19855350</v>
       </c>
     </row>
     <row r="44">
@@ -2248,40 +2248,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>02013</t>
+          <t>09901</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>微盟集团</t>
+          <t>新东方-S</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.46</v>
+        <v>42.02</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.01</v>
+        <v>-0.34</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.68</v>
+        <v>-0.8</v>
       </c>
       <c r="G44" t="n">
-        <v>1.47</v>
+        <v>42.34</v>
       </c>
       <c r="H44" t="n">
-        <v>1.47</v>
+        <v>42.38</v>
       </c>
       <c r="I44" t="n">
-        <v>1.44</v>
+        <v>41.44</v>
       </c>
       <c r="J44" t="n">
-        <v>1.47</v>
+        <v>42.36</v>
       </c>
       <c r="K44" t="n">
-        <v>18872000</v>
+        <v>4983659</v>
       </c>
       <c r="L44" t="n">
-        <v>27487894</v>
+        <v>208667806</v>
       </c>
     </row>
     <row r="45">
@@ -2290,40 +2290,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>06865</t>
+          <t>00027</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>福莱特玻璃</t>
+          <t>银河娱乐</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>33.16</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.77</v>
+        <v>-0.84</v>
       </c>
       <c r="G45" t="n">
-        <v>9.140000000000001</v>
+        <v>33</v>
       </c>
       <c r="H45" t="n">
-        <v>9.220000000000001</v>
+        <v>33.16</v>
       </c>
       <c r="I45" t="n">
-        <v>8.93</v>
+        <v>32.68</v>
       </c>
       <c r="J45" t="n">
-        <v>9.07</v>
+        <v>33.44</v>
       </c>
       <c r="K45" t="n">
-        <v>2238500</v>
+        <v>13290197</v>
       </c>
       <c r="L45" t="n">
-        <v>20223970</v>
+        <v>437814976</v>
       </c>
     </row>
     <row r="46">
@@ -2332,40 +2332,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>00005</t>
+          <t>06186</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>汇丰控股</t>
+          <t>中国飞鹤</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>139.9</v>
+        <v>3.48</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.1</v>
+        <v>-0.03</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.78</v>
+        <v>-0.85</v>
       </c>
       <c r="G46" t="n">
-        <v>139.8</v>
+        <v>3.51</v>
       </c>
       <c r="H46" t="n">
-        <v>141.1</v>
+        <v>3.51</v>
       </c>
       <c r="I46" t="n">
-        <v>139.1</v>
+        <v>3.47</v>
       </c>
       <c r="J46" t="n">
-        <v>141</v>
+        <v>3.51</v>
       </c>
       <c r="K46" t="n">
-        <v>16202407</v>
+        <v>9344800</v>
       </c>
       <c r="L46" t="n">
-        <v>2272311232</v>
+        <v>32605075</v>
       </c>
     </row>
     <row r="47">
@@ -2374,40 +2374,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>06098</t>
+          <t>01833</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>碧桂园服务</t>
+          <t>平安好医生</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6.22</v>
+        <v>10.75</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.8</v>
+        <v>-0.92</v>
       </c>
       <c r="G47" t="n">
-        <v>6.25</v>
+        <v>10.68</v>
       </c>
       <c r="H47" t="n">
-        <v>6.29</v>
+        <v>10.9</v>
       </c>
       <c r="I47" t="n">
-        <v>6.2</v>
+        <v>10.62</v>
       </c>
       <c r="J47" t="n">
-        <v>6.27</v>
+        <v>10.85</v>
       </c>
       <c r="K47" t="n">
-        <v>2772054</v>
+        <v>5498342</v>
       </c>
       <c r="L47" t="n">
-        <v>17312634</v>
+        <v>58937555</v>
       </c>
     </row>
     <row r="48">
@@ -2416,40 +2416,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>06049</t>
+          <t>03900</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>保利物业</t>
+          <t>绿城中国</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>31.16</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.83</v>
+        <v>-0.93</v>
       </c>
       <c r="G48" t="n">
-        <v>31.48</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>31.66</v>
+        <v>9.94</v>
       </c>
       <c r="I48" t="n">
-        <v>31.1</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>31.42</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>597200</v>
+        <v>10360727</v>
       </c>
       <c r="L48" t="n">
-        <v>18698717</v>
+        <v>101097592</v>
       </c>
     </row>
     <row r="49">
@@ -2458,40 +2458,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>09618</t>
+          <t>00941</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>京东集团-SW</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>116.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>-1</v>
+        <v>-0.85</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.85</v>
+        <v>-0.99</v>
       </c>
       <c r="G49" t="n">
-        <v>115.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>117.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>115.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>117.5</v>
+        <v>85.45</v>
       </c>
       <c r="K49" t="n">
-        <v>3121255</v>
+        <v>22743622</v>
       </c>
       <c r="L49" t="n">
-        <v>363139328</v>
+        <v>1925706192</v>
       </c>
     </row>
     <row r="50">
@@ -2500,40 +2500,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01833</t>
+          <t>09888</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>平安好医生</t>
+          <t>百度集团-SW</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.74</v>
+        <v>118.7</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.11</v>
+        <v>-1.2</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.01</v>
+        <v>-1</v>
       </c>
       <c r="G50" t="n">
-        <v>10.68</v>
+        <v>118.6</v>
       </c>
       <c r="H50" t="n">
-        <v>10.9</v>
+        <v>119.8</v>
       </c>
       <c r="I50" t="n">
-        <v>10.62</v>
+        <v>117</v>
       </c>
       <c r="J50" t="n">
-        <v>10.85</v>
+        <v>119.9</v>
       </c>
       <c r="K50" t="n">
-        <v>4868942</v>
+        <v>9556240</v>
       </c>
       <c r="L50" t="n">
-        <v>52174777</v>
+        <v>1131701008</v>
       </c>
     </row>
     <row r="51">
@@ -2542,40 +2542,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>09901</t>
+          <t>09618</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>新东方-S</t>
+          <t>京东集团-SW</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>41.9</v>
+        <v>116.3</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.46</v>
+        <v>-1.2</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.09</v>
+        <v>-1.02</v>
       </c>
       <c r="G51" t="n">
-        <v>42.34</v>
+        <v>115.8</v>
       </c>
       <c r="H51" t="n">
-        <v>42.38</v>
+        <v>117.5</v>
       </c>
       <c r="I51" t="n">
-        <v>41.44</v>
+        <v>115.6</v>
       </c>
       <c r="J51" t="n">
-        <v>42.36</v>
+        <v>117.5</v>
       </c>
       <c r="K51" t="n">
-        <v>3243759</v>
+        <v>5661428</v>
       </c>
       <c r="L51" t="n">
-        <v>135590148</v>
+        <v>658754992</v>
       </c>
     </row>
     <row r="52">
@@ -2584,40 +2584,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>02318</t>
+          <t>02331</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>李宁</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>62.95</v>
+        <v>20.22</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.75</v>
+        <v>-0.22</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.18</v>
+        <v>-1.08</v>
       </c>
       <c r="G52" t="n">
-        <v>63.7</v>
+        <v>20.38</v>
       </c>
       <c r="H52" t="n">
-        <v>64.40000000000001</v>
+        <v>20.74</v>
       </c>
       <c r="I52" t="n">
-        <v>62.9</v>
+        <v>20.1</v>
       </c>
       <c r="J52" t="n">
-        <v>63.7</v>
+        <v>20.44</v>
       </c>
       <c r="K52" t="n">
-        <v>38718491</v>
+        <v>28525339</v>
       </c>
       <c r="L52" t="n">
-        <v>2459841280</v>
+        <v>580781936</v>
       </c>
     </row>
     <row r="53">
@@ -2626,40 +2626,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>06185</t>
+          <t>02318</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>康希诺生物</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>29.48</v>
+        <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.36</v>
+        <v>-0.7</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.21</v>
+        <v>-1.1</v>
       </c>
       <c r="G53" t="n">
-        <v>30</v>
+        <v>63.7</v>
       </c>
       <c r="H53" t="n">
-        <v>30</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>29.24</v>
+        <v>62.85</v>
       </c>
       <c r="J53" t="n">
-        <v>29.84</v>
+        <v>63.7</v>
       </c>
       <c r="K53" t="n">
-        <v>759400</v>
+        <v>50065051</v>
       </c>
       <c r="L53" t="n">
-        <v>22363915</v>
+        <v>3174671488</v>
       </c>
     </row>
     <row r="54">
@@ -2668,40 +2668,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>00762</t>
+          <t>06865</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>中国联通</t>
+          <t>福莱特玻璃</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.33</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.21</v>
+        <v>-1.1</v>
       </c>
       <c r="G54" t="n">
-        <v>7.4</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>7.45</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>7.3</v>
+        <v>8.93</v>
       </c>
       <c r="J54" t="n">
-        <v>7.42</v>
+        <v>9.07</v>
       </c>
       <c r="K54" t="n">
-        <v>14448950</v>
+        <v>2818500</v>
       </c>
       <c r="L54" t="n">
-        <v>106319584</v>
+        <v>25432666</v>
       </c>
     </row>
     <row r="55">
@@ -2710,40 +2710,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>06690</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>海尔智家</t>
+          <t>中国电信</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>21.92</v>
+        <v>5.21</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.28</v>
+        <v>-0.06</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.26</v>
+        <v>-1.14</v>
       </c>
       <c r="G55" t="n">
-        <v>21.92</v>
+        <v>5.27</v>
       </c>
       <c r="H55" t="n">
-        <v>22.32</v>
+        <v>5.27</v>
       </c>
       <c r="I55" t="n">
-        <v>21.92</v>
+        <v>5.18</v>
       </c>
       <c r="J55" t="n">
-        <v>22.2</v>
+        <v>5.27</v>
       </c>
       <c r="K55" t="n">
-        <v>18474062</v>
+        <v>69719636</v>
       </c>
       <c r="L55" t="n">
-        <v>409353872</v>
+        <v>363945568</v>
       </c>
     </row>
     <row r="56">
@@ -2752,40 +2752,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>02331</t>
+          <t>03888</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>李宁</t>
+          <t>金山软件</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>20.18</v>
+        <v>22.8</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.27</v>
+        <v>-1.21</v>
       </c>
       <c r="G56" t="n">
-        <v>20.38</v>
+        <v>22.82</v>
       </c>
       <c r="H56" t="n">
-        <v>20.74</v>
+        <v>23.18</v>
       </c>
       <c r="I56" t="n">
-        <v>20.14</v>
+        <v>22.64</v>
       </c>
       <c r="J56" t="n">
-        <v>20.44</v>
+        <v>23.08</v>
       </c>
       <c r="K56" t="n">
-        <v>19977839</v>
+        <v>8637073</v>
       </c>
       <c r="L56" t="n">
-        <v>408325488</v>
+        <v>196999939</v>
       </c>
     </row>
     <row r="57">
@@ -2794,40 +2794,40 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>00941</t>
+          <t>00520</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>呷哺呷哺</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>84.34999999999999</v>
+        <v>0.405</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.1</v>
+        <v>-0.005</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.29</v>
+        <v>-1.22</v>
       </c>
       <c r="G57" t="n">
-        <v>85.09999999999999</v>
+        <v>0.415</v>
       </c>
       <c r="H57" t="n">
-        <v>85.40000000000001</v>
+        <v>0.425</v>
       </c>
       <c r="I57" t="n">
-        <v>83.59999999999999</v>
+        <v>0.405</v>
       </c>
       <c r="J57" t="n">
-        <v>85.45</v>
+        <v>0.41</v>
       </c>
       <c r="K57" t="n">
-        <v>19845402</v>
+        <v>4353500</v>
       </c>
       <c r="L57" t="n">
-        <v>1680936384</v>
+        <v>1800452</v>
       </c>
     </row>
     <row r="58">
@@ -2836,40 +2836,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>03888</t>
+          <t>00788</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>金山软件</t>
+          <t>中国铁塔</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>22.78</v>
+        <v>11.08</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3</v>
+        <v>-0.14</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.3</v>
+        <v>-1.25</v>
       </c>
       <c r="G58" t="n">
-        <v>22.82</v>
+        <v>11.2</v>
       </c>
       <c r="H58" t="n">
-        <v>23.18</v>
+        <v>11.26</v>
       </c>
       <c r="I58" t="n">
-        <v>22.64</v>
+        <v>11.05</v>
       </c>
       <c r="J58" t="n">
-        <v>23.08</v>
+        <v>11.22</v>
       </c>
       <c r="K58" t="n">
-        <v>6571973</v>
+        <v>9493939</v>
       </c>
       <c r="L58" t="n">
-        <v>149956471</v>
+        <v>105357889</v>
       </c>
     </row>
     <row r="59">
@@ -2878,40 +2878,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>02359</t>
+          <t>06690</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>海尔智家</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>136</v>
+        <v>21.92</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.8</v>
+        <v>-0.28</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.31</v>
+        <v>-1.26</v>
       </c>
       <c r="G59" t="n">
-        <v>137.8</v>
+        <v>21.92</v>
       </c>
       <c r="H59" t="n">
-        <v>139.8</v>
+        <v>22.32</v>
       </c>
       <c r="I59" t="n">
-        <v>134</v>
+        <v>21.88</v>
       </c>
       <c r="J59" t="n">
-        <v>137.8</v>
+        <v>22.2</v>
       </c>
       <c r="K59" t="n">
-        <v>5183387</v>
+        <v>22962372</v>
       </c>
       <c r="L59" t="n">
-        <v>706065280</v>
+        <v>507773360</v>
       </c>
     </row>
     <row r="60">
@@ -2920,40 +2920,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>02359</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>中国电信</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5.2</v>
+        <v>136</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.8</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.33</v>
+        <v>-1.31</v>
       </c>
       <c r="G60" t="n">
-        <v>5.27</v>
+        <v>137.8</v>
       </c>
       <c r="H60" t="n">
-        <v>5.27</v>
+        <v>139.8</v>
       </c>
       <c r="I60" t="n">
-        <v>5.18</v>
+        <v>134</v>
       </c>
       <c r="J60" t="n">
-        <v>5.27</v>
+        <v>137.8</v>
       </c>
       <c r="K60" t="n">
-        <v>63285636</v>
+        <v>6055394</v>
       </c>
       <c r="L60" t="n">
-        <v>330407184</v>
+        <v>824491104</v>
       </c>
     </row>
     <row r="61">
@@ -2962,40 +2962,40 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>03968</t>
+          <t>01579</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>颐海国际</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>47.34</v>
+        <v>16.44</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.64</v>
+        <v>-0.22</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="G61" t="n">
-        <v>47.5</v>
+        <v>16.52</v>
       </c>
       <c r="H61" t="n">
-        <v>47.98</v>
+        <v>16.85</v>
       </c>
       <c r="I61" t="n">
-        <v>47.1</v>
+        <v>16.39</v>
       </c>
       <c r="J61" t="n">
-        <v>47.98</v>
+        <v>16.66</v>
       </c>
       <c r="K61" t="n">
-        <v>20940922</v>
+        <v>1561000</v>
       </c>
       <c r="L61" t="n">
-        <v>993069072</v>
+        <v>25908208</v>
       </c>
     </row>
     <row r="62">
@@ -3004,40 +3004,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>00788</t>
+          <t>00762</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>中国铁塔</t>
+          <t>中国联通</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.07</v>
+        <v>7.32</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.34</v>
+        <v>-1.35</v>
       </c>
       <c r="G62" t="n">
-        <v>11.2</v>
+        <v>7.4</v>
       </c>
       <c r="H62" t="n">
-        <v>11.26</v>
+        <v>7.45</v>
       </c>
       <c r="I62" t="n">
-        <v>11.05</v>
+        <v>7.3</v>
       </c>
       <c r="J62" t="n">
-        <v>11.22</v>
+        <v>7.42</v>
       </c>
       <c r="K62" t="n">
-        <v>5485155</v>
+        <v>17600950</v>
       </c>
       <c r="L62" t="n">
-        <v>60942629</v>
+        <v>129402464</v>
       </c>
     </row>
     <row r="63">
@@ -3046,40 +3046,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>03323</t>
+          <t>01024</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>中国建材</t>
+          <t>快手-W</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5.09</v>
+        <v>42.9</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.62</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.36</v>
+        <v>-1.42</v>
       </c>
       <c r="G63" t="n">
-        <v>5.16</v>
+        <v>42.68</v>
       </c>
       <c r="H63" t="n">
-        <v>5.37</v>
+        <v>43.22</v>
       </c>
       <c r="I63" t="n">
-        <v>5.06</v>
+        <v>42.48</v>
       </c>
       <c r="J63" t="n">
-        <v>5.16</v>
+        <v>43.52</v>
       </c>
       <c r="K63" t="n">
-        <v>28086976</v>
+        <v>25714098</v>
       </c>
       <c r="L63" t="n">
-        <v>145267356</v>
+        <v>1100532640</v>
       </c>
     </row>
     <row r="64">
@@ -3088,40 +3088,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>00027</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>银河娱乐</t>
+          <t>农业银行</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>32.98</v>
+        <v>6.08</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.46</v>
+        <v>-0.09</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.38</v>
+        <v>-1.46</v>
       </c>
       <c r="G64" t="n">
-        <v>33</v>
+        <v>6.17</v>
       </c>
       <c r="H64" t="n">
-        <v>33.16</v>
+        <v>6.3</v>
       </c>
       <c r="I64" t="n">
-        <v>32.68</v>
+        <v>6.05</v>
       </c>
       <c r="J64" t="n">
-        <v>33.44</v>
+        <v>6.17</v>
       </c>
       <c r="K64" t="n">
-        <v>9860197</v>
+        <v>209954895</v>
       </c>
       <c r="L64" t="n">
-        <v>324256944</v>
+        <v>1288803712</v>
       </c>
     </row>
     <row r="65">
@@ -3130,40 +3130,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01024</t>
+          <t>00753</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>快手-W</t>
+          <t>中国国航</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>42.92</v>
+        <v>4.69</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.38</v>
+        <v>-1.47</v>
       </c>
       <c r="G65" t="n">
-        <v>42.68</v>
+        <v>4.78</v>
       </c>
       <c r="H65" t="n">
-        <v>43.22</v>
+        <v>4.78</v>
       </c>
       <c r="I65" t="n">
-        <v>42.48</v>
+        <v>4.57</v>
       </c>
       <c r="J65" t="n">
-        <v>43.52</v>
+        <v>4.76</v>
       </c>
       <c r="K65" t="n">
-        <v>20363688</v>
+        <v>46095786</v>
       </c>
       <c r="L65" t="n">
-        <v>871079664</v>
+        <v>213637066</v>
       </c>
     </row>
     <row r="66">
@@ -3172,40 +3172,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01288</t>
+          <t>00992</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>农业银行</t>
+          <t>联想集团</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6.08</v>
+        <v>11.68</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.09</v>
+        <v>-0.18</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.46</v>
+        <v>-1.52</v>
       </c>
       <c r="G66" t="n">
-        <v>6.17</v>
+        <v>11.78</v>
       </c>
       <c r="H66" t="n">
-        <v>6.3</v>
+        <v>11.89</v>
       </c>
       <c r="I66" t="n">
-        <v>6.06</v>
+        <v>11.53</v>
       </c>
       <c r="J66" t="n">
-        <v>6.17</v>
+        <v>11.86</v>
       </c>
       <c r="K66" t="n">
-        <v>184782475</v>
+        <v>96391543</v>
       </c>
       <c r="L66" t="n">
-        <v>1135962000</v>
+        <v>1125228608</v>
       </c>
     </row>
     <row r="67">
@@ -3214,40 +3214,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01579</t>
+          <t>06185</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>颐海国际</t>
+          <t>康希诺生物</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16.41</v>
+        <v>29.38</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.25</v>
+        <v>-0.46</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.5</v>
+        <v>-1.54</v>
       </c>
       <c r="G67" t="n">
-        <v>16.52</v>
+        <v>30</v>
       </c>
       <c r="H67" t="n">
-        <v>16.85</v>
+        <v>30</v>
       </c>
       <c r="I67" t="n">
-        <v>16.39</v>
+        <v>29.24</v>
       </c>
       <c r="J67" t="n">
-        <v>16.66</v>
+        <v>29.84</v>
       </c>
       <c r="K67" t="n">
-        <v>1226000</v>
+        <v>852200</v>
       </c>
       <c r="L67" t="n">
-        <v>20401843</v>
+        <v>25090035</v>
       </c>
     </row>
     <row r="68">
@@ -3256,40 +3256,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>00992</t>
+          <t>02202</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>联想集团</t>
+          <t>万科企业</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.68</v>
+        <v>2.99</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.18</v>
+        <v>-0.05</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.52</v>
+        <v>-1.64</v>
       </c>
       <c r="G68" t="n">
-        <v>11.78</v>
+        <v>3.04</v>
       </c>
       <c r="H68" t="n">
-        <v>11.89</v>
+        <v>3.05</v>
       </c>
       <c r="I68" t="n">
-        <v>11.53</v>
+        <v>2.96</v>
       </c>
       <c r="J68" t="n">
-        <v>11.86</v>
+        <v>3.04</v>
       </c>
       <c r="K68" t="n">
-        <v>75967543</v>
+        <v>23085769</v>
       </c>
       <c r="L68" t="n">
-        <v>887051568</v>
+        <v>69410788</v>
       </c>
     </row>
     <row r="69">
@@ -3298,40 +3298,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01060</t>
+          <t>06969</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>大麦娱乐</t>
+          <t>思摩尔国际</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.57</v>
+        <v>9.34</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.72</v>
+        <v>-1.68</v>
       </c>
       <c r="G69" t="n">
-        <v>0.58</v>
+        <v>9.5</v>
       </c>
       <c r="H69" t="n">
-        <v>0.58</v>
+        <v>9.5</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5600000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>0.58</v>
+        <v>9.5</v>
       </c>
       <c r="K69" t="n">
-        <v>67131278</v>
+        <v>6365405</v>
       </c>
       <c r="L69" t="n">
-        <v>38443964</v>
+        <v>59397004</v>
       </c>
     </row>
     <row r="70">
@@ -3340,40 +3340,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>02196</t>
+          <t>03323</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>复星医药</t>
+          <t>中国建材</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>19.22</v>
+        <v>5.07</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.36</v>
+        <v>-0.09</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.84</v>
+        <v>-1.74</v>
       </c>
       <c r="G70" t="n">
-        <v>19.58</v>
+        <v>5.16</v>
       </c>
       <c r="H70" t="n">
-        <v>19.58</v>
+        <v>5.37</v>
       </c>
       <c r="I70" t="n">
-        <v>19.03</v>
+        <v>5.06</v>
       </c>
       <c r="J70" t="n">
-        <v>19.58</v>
+        <v>5.16</v>
       </c>
       <c r="K70" t="n">
-        <v>2879735</v>
+        <v>33410976</v>
       </c>
       <c r="L70" t="n">
-        <v>55346491</v>
+        <v>172287442</v>
       </c>
     </row>
     <row r="71">
@@ -3382,40 +3382,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>03998</t>
+          <t>00388</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>波司登</t>
+          <t>香港交易所</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4.26</v>
+        <v>412.4</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.08</v>
+        <v>-7.4</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.84</v>
+        <v>-1.76</v>
       </c>
       <c r="G71" t="n">
-        <v>4.34</v>
+        <v>422</v>
       </c>
       <c r="H71" t="n">
-        <v>4.35</v>
+        <v>427.8</v>
       </c>
       <c r="I71" t="n">
-        <v>4.25</v>
+        <v>411</v>
       </c>
       <c r="J71" t="n">
-        <v>4.34</v>
+        <v>419.8</v>
       </c>
       <c r="K71" t="n">
-        <v>11861106</v>
+        <v>6773830</v>
       </c>
       <c r="L71" t="n">
-        <v>50920875</v>
+        <v>2819563712</v>
       </c>
     </row>
     <row r="72">
@@ -3424,40 +3424,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>00753</t>
+          <t>03968</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>中国国航</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4.67</v>
+        <v>47.1</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.09</v>
+        <v>-0.88</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.89</v>
+        <v>-1.83</v>
       </c>
       <c r="G72" t="n">
-        <v>4.78</v>
+        <v>47.5</v>
       </c>
       <c r="H72" t="n">
-        <v>4.78</v>
+        <v>47.98</v>
       </c>
       <c r="I72" t="n">
-        <v>4.57</v>
+        <v>47.04</v>
       </c>
       <c r="J72" t="n">
-        <v>4.76</v>
+        <v>47.98</v>
       </c>
       <c r="K72" t="n">
-        <v>43981786</v>
+        <v>27203878</v>
       </c>
       <c r="L72" t="n">
-        <v>203743666</v>
+        <v>1288213936</v>
       </c>
     </row>
     <row r="73">
@@ -3466,40 +3466,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>00939</t>
+          <t>03998</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>波司登</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8.82</v>
+        <v>4.26</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.89</v>
+        <v>-1.84</v>
       </c>
       <c r="G73" t="n">
-        <v>9.039999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="H73" t="n">
-        <v>9.050000000000001</v>
+        <v>4.35</v>
       </c>
       <c r="I73" t="n">
-        <v>8.73</v>
+        <v>4.25</v>
       </c>
       <c r="J73" t="n">
-        <v>8.99</v>
+        <v>4.34</v>
       </c>
       <c r="K73" t="n">
-        <v>352237536</v>
+        <v>22019106</v>
       </c>
       <c r="L73" t="n">
-        <v>3129836608</v>
+        <v>94202265</v>
       </c>
     </row>
     <row r="74">
@@ -3508,40 +3508,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>00388</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>香港交易所</t>
+          <t>中远海控</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>411.6</v>
+        <v>14.4</v>
       </c>
       <c r="E74" t="n">
-        <v>-8.199999999999999</v>
+        <v>-0.28</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.95</v>
+        <v>-1.91</v>
       </c>
       <c r="G74" t="n">
-        <v>422</v>
+        <v>14.52</v>
       </c>
       <c r="H74" t="n">
-        <v>427.8</v>
+        <v>14.52</v>
       </c>
       <c r="I74" t="n">
-        <v>411</v>
+        <v>14.21</v>
       </c>
       <c r="J74" t="n">
-        <v>419.8</v>
+        <v>14.68</v>
       </c>
       <c r="K74" t="n">
-        <v>5086174</v>
+        <v>22082948</v>
       </c>
       <c r="L74" t="n">
-        <v>2124384528</v>
+        <v>317187952</v>
       </c>
     </row>
     <row r="75">
@@ -3550,40 +3550,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>02202</t>
+          <t>09698</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>万科企业</t>
+          <t>万国数据-SW</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2.98</v>
+        <v>40.66</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.06</v>
+        <v>-0.82</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.97</v>
+        <v>-1.98</v>
       </c>
       <c r="G75" t="n">
-        <v>3.04</v>
+        <v>41</v>
       </c>
       <c r="H75" t="n">
-        <v>3.05</v>
+        <v>41.38</v>
       </c>
       <c r="I75" t="n">
-        <v>2.96</v>
+        <v>39.66</v>
       </c>
       <c r="J75" t="n">
-        <v>3.04</v>
+        <v>41.48</v>
       </c>
       <c r="K75" t="n">
-        <v>21283069</v>
+        <v>4638289</v>
       </c>
       <c r="L75" t="n">
-        <v>64025851</v>
+        <v>187541031</v>
       </c>
     </row>
     <row r="76">
@@ -3592,40 +3592,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>02018</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>中远海控</t>
+          <t>瑞声科技</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14.39</v>
+        <v>36</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.29</v>
+        <v>-0.78</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.98</v>
+        <v>-2.12</v>
       </c>
       <c r="G76" t="n">
-        <v>14.52</v>
+        <v>36.88</v>
       </c>
       <c r="H76" t="n">
-        <v>14.52</v>
+        <v>36.88</v>
       </c>
       <c r="I76" t="n">
-        <v>14.21</v>
+        <v>35.76</v>
       </c>
       <c r="J76" t="n">
-        <v>14.68</v>
+        <v>36.78</v>
       </c>
       <c r="K76" t="n">
-        <v>18081918</v>
+        <v>6361938</v>
       </c>
       <c r="L76" t="n">
-        <v>259640552</v>
+        <v>228985275</v>
       </c>
     </row>
     <row r="77">
@@ -3634,40 +3634,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>09698</t>
+          <t>02618</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>万国数据-SW</t>
+          <t>京东物流</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>40.66</v>
+        <v>15.1</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.82</v>
+        <v>-0.33</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.98</v>
+        <v>-2.14</v>
       </c>
       <c r="G77" t="n">
-        <v>41</v>
+        <v>15.42</v>
       </c>
       <c r="H77" t="n">
-        <v>41.38</v>
+        <v>15.42</v>
       </c>
       <c r="I77" t="n">
-        <v>39.66</v>
+        <v>15.05</v>
       </c>
       <c r="J77" t="n">
-        <v>41.48</v>
+        <v>15.43</v>
       </c>
       <c r="K77" t="n">
-        <v>2891689</v>
+        <v>9795131</v>
       </c>
       <c r="L77" t="n">
-        <v>116410191</v>
+        <v>148326879</v>
       </c>
     </row>
     <row r="78">
@@ -3676,40 +3676,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01368</t>
+          <t>02899</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>特步国际</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4.32</v>
+        <v>35.68</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.09</v>
+        <v>-0.78</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.04</v>
+        <v>-2.14</v>
       </c>
       <c r="G78" t="n">
-        <v>4.42</v>
+        <v>35.9</v>
       </c>
       <c r="H78" t="n">
-        <v>4.42</v>
+        <v>36.18</v>
       </c>
       <c r="I78" t="n">
-        <v>4.29</v>
+        <v>35.22</v>
       </c>
       <c r="J78" t="n">
-        <v>4.41</v>
+        <v>36.46</v>
       </c>
       <c r="K78" t="n">
-        <v>11702500</v>
+        <v>56435531</v>
       </c>
       <c r="L78" t="n">
-        <v>50666725</v>
+        <v>2008891920</v>
       </c>
     </row>
     <row r="79">
@@ -3718,40 +3718,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>00700</t>
+          <t>02333</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>腾讯控股</t>
+          <t>长城汽车</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>469.4</v>
+        <v>11.6</v>
       </c>
       <c r="E79" t="n">
-        <v>-9.800000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.05</v>
+        <v>-2.19</v>
       </c>
       <c r="G79" t="n">
-        <v>474</v>
+        <v>11.89</v>
       </c>
       <c r="H79" t="n">
-        <v>474.8</v>
+        <v>11.92</v>
       </c>
       <c r="I79" t="n">
-        <v>463.2</v>
+        <v>11.51</v>
       </c>
       <c r="J79" t="n">
-        <v>479.2</v>
+        <v>11.86</v>
       </c>
       <c r="K79" t="n">
-        <v>31922294</v>
+        <v>25942814</v>
       </c>
       <c r="L79" t="n">
-        <v>14948681728</v>
+        <v>302358768</v>
       </c>
     </row>
     <row r="80">
@@ -3760,40 +3760,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>00772</t>
+          <t>00241</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>阅文集团</t>
+          <t>阿里健康</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>24.64</v>
+        <v>4.37</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.52</v>
+        <v>-0.1</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.07</v>
+        <v>-2.24</v>
       </c>
       <c r="G80" t="n">
-        <v>24.9</v>
+        <v>4.45</v>
       </c>
       <c r="H80" t="n">
-        <v>25.14</v>
+        <v>4.45</v>
       </c>
       <c r="I80" t="n">
-        <v>24.38</v>
+        <v>4.36</v>
       </c>
       <c r="J80" t="n">
-        <v>25.16</v>
+        <v>4.47</v>
       </c>
       <c r="K80" t="n">
-        <v>2939483</v>
+        <v>76336762</v>
       </c>
       <c r="L80" t="n">
-        <v>72417052</v>
+        <v>335290320</v>
       </c>
     </row>
     <row r="81">
@@ -3802,40 +3802,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01357</t>
+          <t>03988</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>美图公司</t>
+          <t>中国银行</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4.19</v>
+        <v>5.06</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1</v>
+        <v>-2.32</v>
       </c>
       <c r="G81" t="n">
-        <v>4.24</v>
+        <v>5.15</v>
       </c>
       <c r="H81" t="n">
-        <v>4.26</v>
+        <v>5.18</v>
       </c>
       <c r="I81" t="n">
-        <v>4.17</v>
+        <v>5.05</v>
       </c>
       <c r="J81" t="n">
-        <v>4.28</v>
+        <v>5.18</v>
       </c>
       <c r="K81" t="n">
-        <v>23249004</v>
+        <v>258839216</v>
       </c>
       <c r="L81" t="n">
-        <v>97759429</v>
+        <v>1317768144</v>
       </c>
     </row>
     <row r="82">
@@ -3844,40 +3844,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>03988</t>
+          <t>09626</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>中国银行</t>
+          <t>哔哩哔哩-W</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5.07</v>
+        <v>168.2</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.11</v>
+        <v>-4</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.12</v>
+        <v>-2.32</v>
       </c>
       <c r="G82" t="n">
-        <v>5.15</v>
+        <v>168.6</v>
       </c>
       <c r="H82" t="n">
-        <v>5.18</v>
+        <v>169.4</v>
       </c>
       <c r="I82" t="n">
-        <v>5.05</v>
+        <v>166</v>
       </c>
       <c r="J82" t="n">
-        <v>5.18</v>
+        <v>172.2</v>
       </c>
       <c r="K82" t="n">
-        <v>182953951</v>
+        <v>2155023</v>
       </c>
       <c r="L82" t="n">
-        <v>933684224</v>
+        <v>361749504</v>
       </c>
     </row>
     <row r="83">
@@ -3886,40 +3886,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>02018</t>
+          <t>00939</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>瑞声科技</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>35.98</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.8</v>
+        <v>-0.21</v>
       </c>
       <c r="F83" t="n">
-        <v>-2.18</v>
+        <v>-2.34</v>
       </c>
       <c r="G83" t="n">
-        <v>36.88</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>36.88</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>35.76</v>
+        <v>8.73</v>
       </c>
       <c r="J83" t="n">
-        <v>36.78</v>
+        <v>8.99</v>
       </c>
       <c r="K83" t="n">
-        <v>4794938</v>
+        <v>424520912</v>
       </c>
       <c r="L83" t="n">
-        <v>172662335</v>
+        <v>3764834960</v>
       </c>
     </row>
     <row r="84">
@@ -3928,40 +3928,40 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>00700</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>心动公司</t>
+          <t>腾讯控股</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>62.7</v>
+        <v>467.8</v>
       </c>
       <c r="E84" t="n">
-        <v>-1.4</v>
+        <v>-11.4</v>
       </c>
       <c r="F84" t="n">
-        <v>-2.18</v>
+        <v>-2.38</v>
       </c>
       <c r="G84" t="n">
-        <v>63.9</v>
+        <v>474</v>
       </c>
       <c r="H84" t="n">
-        <v>64.40000000000001</v>
+        <v>474.8</v>
       </c>
       <c r="I84" t="n">
-        <v>61.9</v>
+        <v>463.2</v>
       </c>
       <c r="J84" t="n">
-        <v>64.09999999999999</v>
+        <v>479.2</v>
       </c>
       <c r="K84" t="n">
-        <v>1702721</v>
+        <v>38406905</v>
       </c>
       <c r="L84" t="n">
-        <v>106699299</v>
+        <v>17984606464</v>
       </c>
     </row>
     <row r="85">
@@ -3970,40 +3970,40 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>06969</t>
+          <t>00772</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>思摩尔国际</t>
+          <t>阅文集团</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>9.289999999999999</v>
+        <v>24.56</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="F85" t="n">
-        <v>-2.21</v>
+        <v>-2.38</v>
       </c>
       <c r="G85" t="n">
-        <v>9.5</v>
+        <v>24.9</v>
       </c>
       <c r="H85" t="n">
-        <v>9.5</v>
+        <v>25.14</v>
       </c>
       <c r="I85" t="n">
-        <v>9.220000000000001</v>
+        <v>24.38</v>
       </c>
       <c r="J85" t="n">
-        <v>9.5</v>
+        <v>25.16</v>
       </c>
       <c r="K85" t="n">
-        <v>5036405</v>
+        <v>3334683</v>
       </c>
       <c r="L85" t="n">
-        <v>47014979</v>
+        <v>82137304</v>
       </c>
     </row>
     <row r="86">
@@ -4012,40 +4012,40 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01398</t>
+          <t>09868</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>工商银行</t>
+          <t>小鹏集团-W</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>7.06</v>
+        <v>61</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.16</v>
+        <v>-1.5</v>
       </c>
       <c r="F86" t="n">
-        <v>-2.22</v>
+        <v>-2.4</v>
       </c>
       <c r="G86" t="n">
-        <v>7.13</v>
+        <v>61.7</v>
       </c>
       <c r="H86" t="n">
-        <v>7.23</v>
+        <v>62.5</v>
       </c>
       <c r="I86" t="n">
-        <v>7.01</v>
+        <v>60.85</v>
       </c>
       <c r="J86" t="n">
-        <v>7.22</v>
+        <v>62.5</v>
       </c>
       <c r="K86" t="n">
-        <v>375271984</v>
+        <v>12382691</v>
       </c>
       <c r="L86" t="n">
-        <v>2661316704</v>
+        <v>759157728</v>
       </c>
     </row>
     <row r="87">
@@ -4054,40 +4054,40 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>00241</t>
+          <t>02196</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>阿里健康</t>
+          <t>复星医药</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4.37</v>
+        <v>19.11</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.1</v>
+        <v>-0.47</v>
       </c>
       <c r="F87" t="n">
-        <v>-2.24</v>
+        <v>-2.4</v>
       </c>
       <c r="G87" t="n">
-        <v>4.45</v>
+        <v>19.58</v>
       </c>
       <c r="H87" t="n">
-        <v>4.45</v>
+        <v>19.58</v>
       </c>
       <c r="I87" t="n">
-        <v>4.36</v>
+        <v>19.03</v>
       </c>
       <c r="J87" t="n">
-        <v>4.47</v>
+        <v>19.58</v>
       </c>
       <c r="K87" t="n">
-        <v>66520762</v>
+        <v>3528235</v>
       </c>
       <c r="L87" t="n">
-        <v>292365456</v>
+        <v>67817647</v>
       </c>
     </row>
     <row r="88">
@@ -4096,40 +4096,40 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01929</t>
+          <t>02015</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>理想汽车-W</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.71</v>
+        <v>67.55</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.25</v>
+        <v>-1.7</v>
       </c>
       <c r="F88" t="n">
-        <v>-2.28</v>
+        <v>-2.45</v>
       </c>
       <c r="G88" t="n">
-        <v>10.96</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>10.96</v>
+        <v>69.75</v>
       </c>
       <c r="I88" t="n">
-        <v>10.69</v>
+        <v>67.3</v>
       </c>
       <c r="J88" t="n">
-        <v>10.96</v>
+        <v>69.25</v>
       </c>
       <c r="K88" t="n">
-        <v>18913746</v>
+        <v>9614488</v>
       </c>
       <c r="L88" t="n">
-        <v>204279027</v>
+        <v>653745136</v>
       </c>
     </row>
     <row r="89">
@@ -4138,40 +4138,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>00914</t>
+          <t>02020</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>海螺水泥</t>
+          <t>安踏体育</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>19.62</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.46</v>
+        <v>-2.05</v>
       </c>
       <c r="F89" t="n">
-        <v>-2.29</v>
+        <v>-2.46</v>
       </c>
       <c r="G89" t="n">
-        <v>19.74</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>19.83</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>19.51</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>20.08</v>
+        <v>83.2</v>
       </c>
       <c r="K89" t="n">
-        <v>8603113</v>
+        <v>8725796</v>
       </c>
       <c r="L89" t="n">
-        <v>168982867</v>
+        <v>713985584</v>
       </c>
     </row>
     <row r="90">
@@ -4180,40 +4180,40 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>02020</t>
+          <t>00780</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>安踏体育</t>
+          <t>同程旅行</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>81.25</v>
+        <v>17.75</v>
       </c>
       <c r="E90" t="n">
-        <v>-1.95</v>
+        <v>-0.46</v>
       </c>
       <c r="F90" t="n">
-        <v>-2.34</v>
+        <v>-2.53</v>
       </c>
       <c r="G90" t="n">
-        <v>82.84999999999999</v>
+        <v>17.97</v>
       </c>
       <c r="H90" t="n">
-        <v>83.40000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="I90" t="n">
-        <v>80.90000000000001</v>
+        <v>17.59</v>
       </c>
       <c r="J90" t="n">
-        <v>83.2</v>
+        <v>18.21</v>
       </c>
       <c r="K90" t="n">
-        <v>6634196</v>
+        <v>5752661</v>
       </c>
       <c r="L90" t="n">
-        <v>544240880</v>
+        <v>101970051</v>
       </c>
     </row>
     <row r="91">
@@ -4222,40 +4222,40 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>02269</t>
+          <t>02150</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>药明生物</t>
+          <t>奈雪的茶</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>33.14</v>
+        <v>0.77</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.8</v>
+        <v>-0.02</v>
       </c>
       <c r="F91" t="n">
-        <v>-2.36</v>
+        <v>-2.53</v>
       </c>
       <c r="G91" t="n">
-        <v>33.62</v>
+        <v>0.77</v>
       </c>
       <c r="H91" t="n">
-        <v>33.82</v>
+        <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>32.8</v>
+        <v>0.75</v>
       </c>
       <c r="J91" t="n">
-        <v>33.94</v>
+        <v>0.79</v>
       </c>
       <c r="K91" t="n">
-        <v>28828739</v>
+        <v>3399500</v>
       </c>
       <c r="L91" t="n">
-        <v>952763584</v>
+        <v>2591465</v>
       </c>
     </row>
     <row r="92">
@@ -4264,40 +4264,40 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>02618</t>
+          <t>06618</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>京东物流</t>
+          <t>京东健康</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>15.06</v>
+        <v>45.36</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.37</v>
+        <v>-1.2</v>
       </c>
       <c r="F92" t="n">
-        <v>-2.4</v>
+        <v>-2.58</v>
       </c>
       <c r="G92" t="n">
-        <v>15.42</v>
+        <v>45.66</v>
       </c>
       <c r="H92" t="n">
-        <v>15.42</v>
+        <v>46.46</v>
       </c>
       <c r="I92" t="n">
-        <v>15.05</v>
+        <v>45.04</v>
       </c>
       <c r="J92" t="n">
-        <v>15.43</v>
+        <v>46.56</v>
       </c>
       <c r="K92" t="n">
-        <v>6551731</v>
+        <v>8129118</v>
       </c>
       <c r="L92" t="n">
-        <v>99372052</v>
+        <v>369765680</v>
       </c>
     </row>
     <row r="93">
@@ -4306,40 +4306,40 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>09868</t>
+          <t>00914</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>小鹏集团-W</t>
+          <t>海螺水泥</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>61</v>
+        <v>19.56</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.5</v>
+        <v>-0.52</v>
       </c>
       <c r="F93" t="n">
-        <v>-2.4</v>
+        <v>-2.59</v>
       </c>
       <c r="G93" t="n">
-        <v>61.7</v>
+        <v>19.74</v>
       </c>
       <c r="H93" t="n">
-        <v>62.5</v>
+        <v>19.83</v>
       </c>
       <c r="I93" t="n">
-        <v>60.85</v>
+        <v>19.51</v>
       </c>
       <c r="J93" t="n">
-        <v>62.5</v>
+        <v>20.08</v>
       </c>
       <c r="K93" t="n">
-        <v>9891880</v>
+        <v>10817283</v>
       </c>
       <c r="L93" t="n">
-        <v>607235296</v>
+        <v>212338758</v>
       </c>
     </row>
     <row r="94">
@@ -4348,40 +4348,40 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>00780</t>
+          <t>01398</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>同程旅行</t>
+          <t>工商银行</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>17.75</v>
+        <v>7.03</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.46</v>
+        <v>-0.19</v>
       </c>
       <c r="F94" t="n">
-        <v>-2.53</v>
+        <v>-2.63</v>
       </c>
       <c r="G94" t="n">
-        <v>17.97</v>
+        <v>7.13</v>
       </c>
       <c r="H94" t="n">
-        <v>18.2</v>
+        <v>7.23</v>
       </c>
       <c r="I94" t="n">
-        <v>17.59</v>
+        <v>7.01</v>
       </c>
       <c r="J94" t="n">
-        <v>18.21</v>
+        <v>7.22</v>
       </c>
       <c r="K94" t="n">
-        <v>4421261</v>
+        <v>473345024</v>
       </c>
       <c r="L94" t="n">
-        <v>78337774</v>
+        <v>3351499088</v>
       </c>
     </row>
     <row r="95">
@@ -4390,40 +4390,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>02015</t>
+          <t>02269</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>理想汽车-W</t>
+          <t>药明生物</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>67.5</v>
+        <v>33.04</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.75</v>
+        <v>-0.9</v>
       </c>
       <c r="F95" t="n">
-        <v>-2.53</v>
+        <v>-2.65</v>
       </c>
       <c r="G95" t="n">
-        <v>68.59999999999999</v>
+        <v>33.62</v>
       </c>
       <c r="H95" t="n">
-        <v>69.75</v>
+        <v>33.82</v>
       </c>
       <c r="I95" t="n">
-        <v>67.3</v>
+        <v>32.8</v>
       </c>
       <c r="J95" t="n">
-        <v>69.25</v>
+        <v>33.94</v>
       </c>
       <c r="K95" t="n">
-        <v>7478198</v>
+        <v>34158572</v>
       </c>
       <c r="L95" t="n">
-        <v>509481504</v>
+        <v>1128738032</v>
       </c>
     </row>
     <row r="96">
@@ -4432,40 +4432,40 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>09626</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>哔哩哔哩-W</t>
+          <t>心动公司</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>167.7</v>
+        <v>62.4</v>
       </c>
       <c r="E96" t="n">
-        <v>-4.5</v>
+        <v>-1.7</v>
       </c>
       <c r="F96" t="n">
-        <v>-2.61</v>
+        <v>-2.65</v>
       </c>
       <c r="G96" t="n">
-        <v>168.6</v>
+        <v>63.9</v>
       </c>
       <c r="H96" t="n">
-        <v>169.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>166</v>
+        <v>61.9</v>
       </c>
       <c r="J96" t="n">
-        <v>172.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K96" t="n">
-        <v>1586083</v>
+        <v>2050721</v>
       </c>
       <c r="L96" t="n">
-        <v>266165196</v>
+        <v>128461479</v>
       </c>
     </row>
     <row r="97">
@@ -4474,40 +4474,40 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>06618</t>
+          <t>03328</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>京东健康</t>
+          <t>交通银行</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>45.34</v>
+        <v>7.15</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.22</v>
+        <v>-0.2</v>
       </c>
       <c r="F97" t="n">
-        <v>-2.62</v>
+        <v>-2.72</v>
       </c>
       <c r="G97" t="n">
-        <v>45.66</v>
+        <v>7.39</v>
       </c>
       <c r="H97" t="n">
-        <v>46.46</v>
+        <v>7.39</v>
       </c>
       <c r="I97" t="n">
-        <v>45.04</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
-        <v>46.56</v>
+        <v>7.35</v>
       </c>
       <c r="K97" t="n">
-        <v>5701218</v>
+        <v>110349146</v>
       </c>
       <c r="L97" t="n">
-        <v>259633443</v>
+        <v>789471504</v>
       </c>
     </row>
     <row r="98">
@@ -4516,40 +4516,40 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>02333</t>
+          <t>01357</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>长城汽车</t>
+          <t>美图公司</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.54</v>
+        <v>4.16</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.32</v>
+        <v>-0.12</v>
       </c>
       <c r="F98" t="n">
-        <v>-2.7</v>
+        <v>-2.8</v>
       </c>
       <c r="G98" t="n">
-        <v>11.89</v>
+        <v>4.24</v>
       </c>
       <c r="H98" t="n">
-        <v>11.92</v>
+        <v>4.26</v>
       </c>
       <c r="I98" t="n">
-        <v>11.51</v>
+        <v>4.15</v>
       </c>
       <c r="J98" t="n">
-        <v>11.86</v>
+        <v>4.28</v>
       </c>
       <c r="K98" t="n">
-        <v>19030444</v>
+        <v>28858504</v>
       </c>
       <c r="L98" t="n">
-        <v>222263258</v>
+        <v>121134636</v>
       </c>
     </row>
     <row r="99">
@@ -4558,40 +4558,40 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>03328</t>
+          <t>09633</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>交通银行</t>
+          <t>农夫山泉</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>7.15</v>
+        <v>46.8</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.2</v>
+        <v>-1.38</v>
       </c>
       <c r="F99" t="n">
-        <v>-2.72</v>
+        <v>-2.86</v>
       </c>
       <c r="G99" t="n">
-        <v>7.39</v>
+        <v>47.6</v>
       </c>
       <c r="H99" t="n">
-        <v>7.39</v>
+        <v>48.08</v>
       </c>
       <c r="I99" t="n">
-        <v>7</v>
+        <v>46.58</v>
       </c>
       <c r="J99" t="n">
-        <v>7.35</v>
+        <v>48.18</v>
       </c>
       <c r="K99" t="n">
-        <v>65967229</v>
+        <v>9634815</v>
       </c>
       <c r="L99" t="n">
-        <v>472216096</v>
+        <v>452686720</v>
       </c>
     </row>
     <row r="100">
@@ -4600,40 +4600,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>02899</t>
+          <t>01138</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>中远海能</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>35.46</v>
+        <v>18.24</v>
       </c>
       <c r="E100" t="n">
-        <v>-1</v>
+        <v>-0.54</v>
       </c>
       <c r="F100" t="n">
-        <v>-2.74</v>
+        <v>-2.88</v>
       </c>
       <c r="G100" t="n">
-        <v>35.9</v>
+        <v>18.52</v>
       </c>
       <c r="H100" t="n">
-        <v>36.18</v>
+        <v>18.7</v>
       </c>
       <c r="I100" t="n">
-        <v>35.22</v>
+        <v>18.05</v>
       </c>
       <c r="J100" t="n">
-        <v>36.46</v>
+        <v>18.78</v>
       </c>
       <c r="K100" t="n">
-        <v>36045031</v>
+        <v>20692000</v>
       </c>
       <c r="L100" t="n">
-        <v>1282534640</v>
+        <v>378405376</v>
       </c>
     </row>
     <row r="101">
@@ -4642,40 +4642,40 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01810</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>小米集团-W</t>
+          <t>大唐发电</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>29.26</v>
+        <v>2.7</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.88</v>
+        <v>-0.08</v>
       </c>
       <c r="F101" t="n">
-        <v>-2.92</v>
+        <v>-2.88</v>
       </c>
       <c r="G101" t="n">
-        <v>29.82</v>
+        <v>2.76</v>
       </c>
       <c r="H101" t="n">
-        <v>29.88</v>
+        <v>2.78</v>
       </c>
       <c r="I101" t="n">
-        <v>28.8</v>
+        <v>2.67</v>
       </c>
       <c r="J101" t="n">
-        <v>30.14</v>
+        <v>2.78</v>
       </c>
       <c r="K101" t="n">
-        <v>245776409</v>
+        <v>42424183</v>
       </c>
       <c r="L101" t="n">
-        <v>7165797632</v>
+        <v>114920683</v>
       </c>
     </row>
   </sheetData>
